--- a/research/traditional_assets/database/data/turkey/turkey_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_real_estate_general_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1002947629207248</v>
+        <v>0.100077776013423</v>
       </c>
       <c r="C2">
-        <v>103.2705451971858</v>
+        <v>102.8665966834775</v>
       </c>
       <c r="D2">
-        <v>100.8205451971858</v>
+        <v>101.2235966834775</v>
       </c>
       <c r="E2">
-        <v>-41.1</v>
+        <v>-40.293</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G2">
         <v>2.45</v>
@@ -1445,28 +1445,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0405921</v>
       </c>
       <c r="N2">
-        <v>8.953333333333333</v>
+        <v>8.912741233333334</v>
       </c>
       <c r="O2">
-        <v>2.238333333333333</v>
+        <v>2.228185308333333</v>
       </c>
       <c r="P2">
-        <v>6.715</v>
+        <v>6.684555925</v>
       </c>
       <c r="Q2">
-        <v>6.845</v>
+        <v>6.814555925</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1002947629207248</v>
+        <v>0.1007076020337606</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5309984765800596</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>220.5683700358773</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.100077776013423</v>
+        <v>0.09986078910612117</v>
       </c>
       <c r="C3">
-        <v>102.8665966834775</v>
+        <v>102.4658836717639</v>
       </c>
       <c r="D3">
-        <v>101.2235966834775</v>
+        <v>101.6298836717639</v>
       </c>
       <c r="E3">
-        <v>-40.293</v>
+        <v>-39.486</v>
       </c>
       <c r="F3">
-        <v>0.8070000000000001</v>
+        <v>1.614</v>
       </c>
       <c r="G3">
         <v>2.45</v>
@@ -1527,28 +1527,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M3">
-        <v>0.0405921</v>
+        <v>0.0811842</v>
       </c>
       <c r="N3">
-        <v>8.912741233333334</v>
+        <v>8.872149133333334</v>
       </c>
       <c r="O3">
-        <v>2.228185308333333</v>
+        <v>2.218037283333333</v>
       </c>
       <c r="P3">
-        <v>6.684555925</v>
+        <v>6.65411185</v>
       </c>
       <c r="Q3">
-        <v>6.814555925</v>
+        <v>6.78411185</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1007076020337606</v>
+        <v>0.1011288664348175</v>
       </c>
       <c r="T3">
-        <v>0.5309984765800596</v>
+        <v>0.5350724253032456</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>220.5683700358773</v>
+        <v>110.2841850179386</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09986078910612117</v>
+        <v>0.09964380219881934</v>
       </c>
       <c r="C4">
-        <v>102.4658836717639</v>
+        <v>102.0684452786124</v>
       </c>
       <c r="D4">
-        <v>101.6298836717639</v>
+        <v>102.0394452786124</v>
       </c>
       <c r="E4">
-        <v>-39.486</v>
+        <v>-38.679</v>
       </c>
       <c r="F4">
-        <v>1.614</v>
+        <v>2.421</v>
       </c>
       <c r="G4">
         <v>2.45</v>
@@ -1609,28 +1609,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M4">
-        <v>0.0811842</v>
+        <v>0.1217763</v>
       </c>
       <c r="N4">
-        <v>8.872149133333334</v>
+        <v>8.831557033333333</v>
       </c>
       <c r="O4">
-        <v>2.218037283333333</v>
+        <v>2.207889258333333</v>
       </c>
       <c r="P4">
-        <v>6.65411185</v>
+        <v>6.623667774999999</v>
       </c>
       <c r="Q4">
-        <v>6.78411185</v>
+        <v>6.753667774999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1011288664348175</v>
+        <v>0.1015588166998138</v>
       </c>
       <c r="T4">
-        <v>0.5350724253032456</v>
+        <v>0.5392303729691776</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.2841850179386</v>
+        <v>73.52279001195909</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09964380219881934</v>
+        <v>0.09942681529151753</v>
       </c>
       <c r="C5">
-        <v>102.0684452786124</v>
+        <v>101.6743212536901</v>
       </c>
       <c r="D5">
-        <v>102.0394452786124</v>
+        <v>102.4523212536901</v>
       </c>
       <c r="E5">
-        <v>-38.679</v>
+        <v>-37.872</v>
       </c>
       <c r="F5">
-        <v>2.421</v>
+        <v>3.228</v>
       </c>
       <c r="G5">
         <v>2.45</v>
@@ -1691,28 +1691,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M5">
-        <v>0.1217763</v>
+        <v>0.1623684</v>
       </c>
       <c r="N5">
-        <v>8.831557033333333</v>
+        <v>8.790964933333333</v>
       </c>
       <c r="O5">
-        <v>2.207889258333333</v>
+        <v>2.197741233333333</v>
       </c>
       <c r="P5">
-        <v>6.623667774999999</v>
+        <v>6.593223699999999</v>
       </c>
       <c r="Q5">
-        <v>6.753667774999999</v>
+        <v>6.723223699999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1015588166998138</v>
+        <v>0.1019977242619974</v>
       </c>
       <c r="T5">
-        <v>0.5392303729691776</v>
+        <v>0.5434749445448166</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.52279001195909</v>
+        <v>55.14209250896931</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09942681529151753</v>
+        <v>0.09920982838421573</v>
       </c>
       <c r="C6">
-        <v>101.6743212536901</v>
+        <v>101.2835519926247</v>
       </c>
       <c r="D6">
-        <v>102.4523212536901</v>
+        <v>102.8685519926247</v>
       </c>
       <c r="E6">
-        <v>-37.872</v>
+        <v>-37.065</v>
       </c>
       <c r="F6">
-        <v>3.228</v>
+        <v>4.035</v>
       </c>
       <c r="G6">
         <v>2.45</v>
@@ -1773,28 +1773,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M6">
-        <v>0.1623684</v>
+        <v>0.2029605</v>
       </c>
       <c r="N6">
-        <v>8.790964933333333</v>
+        <v>8.750372833333333</v>
       </c>
       <c r="O6">
-        <v>2.197741233333333</v>
+        <v>2.187593208333333</v>
       </c>
       <c r="P6">
-        <v>6.593223699999999</v>
+        <v>6.562779625</v>
       </c>
       <c r="Q6">
-        <v>6.723223699999999</v>
+        <v>6.692779625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1019977242619974</v>
+        <v>0.102445871983385</v>
       </c>
       <c r="T6">
-        <v>0.5434749445448166</v>
+        <v>0.547808875522048</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.14209250896931</v>
+        <v>44.11367400717545</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09920982838421573</v>
+        <v>0.09899284147691391</v>
       </c>
       <c r="C7">
-        <v>101.2835519926247</v>
+        <v>100.8961785501791</v>
       </c>
       <c r="D7">
-        <v>102.8685519926247</v>
+        <v>103.2881785501791</v>
       </c>
       <c r="E7">
-        <v>-37.065</v>
+        <v>-36.258</v>
       </c>
       <c r="F7">
-        <v>4.035</v>
+        <v>4.842000000000001</v>
       </c>
       <c r="G7">
         <v>2.45</v>
@@ -1855,28 +1855,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M7">
-        <v>0.2029605</v>
+        <v>0.2435526</v>
       </c>
       <c r="N7">
-        <v>8.750372833333333</v>
+        <v>8.709780733333334</v>
       </c>
       <c r="O7">
-        <v>2.187593208333333</v>
+        <v>2.177445183333333</v>
       </c>
       <c r="P7">
-        <v>6.562779625</v>
+        <v>6.532335550000001</v>
       </c>
       <c r="Q7">
-        <v>6.692779625</v>
+        <v>6.662335550000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.102445871983385</v>
+        <v>0.1029035547626744</v>
       </c>
       <c r="T7">
-        <v>0.547808875522048</v>
+        <v>0.5522350177966673</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.11367400717545</v>
+        <v>36.76139500597954</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09899284147691391</v>
+        <v>0.0987758545696121</v>
       </c>
       <c r="C8">
-        <v>100.8961785501791</v>
+        <v>100.5122426537509</v>
       </c>
       <c r="D8">
-        <v>103.2881785501791</v>
+        <v>103.7112426537509</v>
       </c>
       <c r="E8">
-        <v>-36.258</v>
+        <v>-35.451</v>
       </c>
       <c r="F8">
-        <v>4.842</v>
+        <v>5.649</v>
       </c>
       <c r="G8">
         <v>2.45</v>
@@ -1937,28 +1937,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M8">
-        <v>0.2435526</v>
+        <v>0.2841447</v>
       </c>
       <c r="N8">
-        <v>8.709780733333334</v>
+        <v>8.669188633333333</v>
       </c>
       <c r="O8">
-        <v>2.177445183333333</v>
+        <v>2.167297158333333</v>
       </c>
       <c r="P8">
-        <v>6.532335550000001</v>
+        <v>6.501891474999999</v>
       </c>
       <c r="Q8">
-        <v>6.662335550000001</v>
+        <v>6.631891474999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1029035547626744</v>
+        <v>0.1033710801823786</v>
       </c>
       <c r="T8">
-        <v>0.5522350177966673</v>
+        <v>0.5567563459266548</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.76139500597955</v>
+        <v>31.50976714798247</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09877585456961209</v>
+        <v>0.09855886766231028</v>
       </c>
       <c r="C9">
-        <v>100.5122426537509</v>
+        <v>100.131786717204</v>
       </c>
       <c r="D9">
-        <v>103.7112426537509</v>
+        <v>104.137786717204</v>
       </c>
       <c r="E9">
-        <v>-35.451</v>
+        <v>-34.644</v>
       </c>
       <c r="F9">
-        <v>5.649000000000001</v>
+        <v>6.456</v>
       </c>
       <c r="G9">
         <v>2.45</v>
@@ -2019,28 +2019,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M9">
-        <v>0.2841447</v>
+        <v>0.3247368</v>
       </c>
       <c r="N9">
-        <v>8.669188633333333</v>
+        <v>8.628596533333333</v>
       </c>
       <c r="O9">
-        <v>2.167297158333333</v>
+        <v>2.157149133333333</v>
       </c>
       <c r="P9">
-        <v>6.501891474999999</v>
+        <v>6.4714474</v>
       </c>
       <c r="Q9">
-        <v>6.631891474999999</v>
+        <v>6.6014474</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1033710801823786</v>
+        <v>0.1038487691981634</v>
       </c>
       <c r="T9">
-        <v>0.5567563459266548</v>
+        <v>0.5613759637985986</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.50976714798246</v>
+        <v>27.57104625448466</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09855886766231028</v>
+        <v>0.09834188075500849</v>
       </c>
       <c r="C10">
-        <v>100.131786717204</v>
+        <v>99.75485385504362</v>
       </c>
       <c r="D10">
-        <v>104.137786717204</v>
+        <v>104.5678538550436</v>
       </c>
       <c r="E10">
-        <v>-34.644</v>
+        <v>-33.837</v>
       </c>
       <c r="F10">
-        <v>6.456</v>
+        <v>7.263</v>
       </c>
       <c r="G10">
         <v>2.45</v>
@@ -2101,28 +2101,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M10">
-        <v>0.3247368</v>
+        <v>0.3653289</v>
       </c>
       <c r="N10">
-        <v>8.628596533333333</v>
+        <v>8.588004433333333</v>
       </c>
       <c r="O10">
-        <v>2.157149133333333</v>
+        <v>2.147001108333333</v>
       </c>
       <c r="P10">
-        <v>6.4714474</v>
+        <v>6.441003325000001</v>
       </c>
       <c r="Q10">
-        <v>6.6014474</v>
+        <v>6.571003325</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1038487691981634</v>
+        <v>0.1043369568736357</v>
       </c>
       <c r="T10">
-        <v>0.5613759637985986</v>
+        <v>0.5660971117336618</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.57104625448466</v>
+        <v>24.50759667065303</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09834188075500849</v>
+        <v>0.09812489384770666</v>
       </c>
       <c r="C11">
-        <v>99.75485385504362</v>
+        <v>99.38148789694412</v>
       </c>
       <c r="D11">
-        <v>104.5678538550436</v>
+        <v>105.0014878969441</v>
       </c>
       <c r="E11">
-        <v>-33.837</v>
+        <v>-33.03</v>
       </c>
       <c r="F11">
-        <v>7.263</v>
+        <v>8.07</v>
       </c>
       <c r="G11">
         <v>2.45</v>
@@ -2183,28 +2183,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M11">
-        <v>0.3653289</v>
+        <v>0.405921</v>
       </c>
       <c r="N11">
-        <v>8.588004433333333</v>
+        <v>8.547412333333334</v>
       </c>
       <c r="O11">
-        <v>2.147001108333333</v>
+        <v>2.136853083333333</v>
       </c>
       <c r="P11">
-        <v>6.441003325000001</v>
+        <v>6.41055925</v>
       </c>
       <c r="Q11">
-        <v>6.571003325</v>
+        <v>6.54055925</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1043369568736357</v>
+        <v>0.1048359931641185</v>
       </c>
       <c r="T11">
-        <v>0.5660971117336618</v>
+        <v>0.5709231740672821</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.50759667065303</v>
+        <v>22.05683700358773</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09812489384770666</v>
+        <v>0.09790790694040484</v>
       </c>
       <c r="C12">
-        <v>99.38148789694412</v>
+        <v>99.01173340263878</v>
       </c>
       <c r="D12">
-        <v>105.0014878969441</v>
+        <v>105.4387334026388</v>
       </c>
       <c r="E12">
-        <v>-33.03</v>
+        <v>-32.223</v>
       </c>
       <c r="F12">
-        <v>8.07</v>
+        <v>8.877000000000001</v>
       </c>
       <c r="G12">
         <v>2.45</v>
@@ -2265,28 +2265,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M12">
-        <v>0.405921</v>
+        <v>0.4465131</v>
       </c>
       <c r="N12">
-        <v>8.547412333333334</v>
+        <v>8.506820233333332</v>
       </c>
       <c r="O12">
-        <v>2.136853083333333</v>
+        <v>2.126705058333333</v>
       </c>
       <c r="P12">
-        <v>6.41055925</v>
+        <v>6.380115174999999</v>
       </c>
       <c r="Q12">
-        <v>6.54055925</v>
+        <v>6.510115174999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1048359931641185</v>
+        <v>0.1053462437532639</v>
       </c>
       <c r="T12">
-        <v>0.5709231740672821</v>
+        <v>0.5758576872398602</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.05683700358773</v>
+        <v>20.05167000326157</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09790790694040484</v>
+        <v>0.09769092003310305</v>
       </c>
       <c r="C13">
-        <v>99.01173340263878</v>
+        <v>98.64563567718434</v>
       </c>
       <c r="D13">
-        <v>105.4387334026388</v>
+        <v>105.8796356771843</v>
       </c>
       <c r="E13">
-        <v>-32.223</v>
+        <v>-31.416</v>
       </c>
       <c r="F13">
-        <v>8.877000000000001</v>
+        <v>9.683999999999999</v>
       </c>
       <c r="G13">
         <v>2.45</v>
@@ -2347,28 +2347,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M13">
-        <v>0.4465131</v>
+        <v>0.4871052</v>
       </c>
       <c r="N13">
-        <v>8.506820233333332</v>
+        <v>8.466228133333333</v>
       </c>
       <c r="O13">
-        <v>2.126705058333333</v>
+        <v>2.116557033333333</v>
       </c>
       <c r="P13">
-        <v>6.380115174999999</v>
+        <v>6.3496711</v>
       </c>
       <c r="Q13">
-        <v>6.510115174999999</v>
+        <v>6.4796711</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1053462437532639</v>
+        <v>0.105868090946708</v>
       </c>
       <c r="T13">
-        <v>0.5758576872398602</v>
+        <v>0.5809043484390878</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.05167000326157</v>
+        <v>18.38069750298977</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09769092003310305</v>
+        <v>0.09747393312580122</v>
       </c>
       <c r="C14">
-        <v>98.64563567718434</v>
+        <v>98.28324078660974</v>
       </c>
       <c r="D14">
-        <v>105.8796356771843</v>
+        <v>106.3242407866097</v>
       </c>
       <c r="E14">
-        <v>-31.416</v>
+        <v>-30.609</v>
       </c>
       <c r="F14">
-        <v>9.683999999999999</v>
+        <v>10.491</v>
       </c>
       <c r="G14">
         <v>2.45</v>
@@ -2429,28 +2429,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M14">
-        <v>0.4871052</v>
+        <v>0.5276973</v>
       </c>
       <c r="N14">
-        <v>8.466228133333333</v>
+        <v>8.425636033333333</v>
       </c>
       <c r="O14">
-        <v>2.116557033333333</v>
+        <v>2.106409008333333</v>
       </c>
       <c r="P14">
-        <v>6.3496711</v>
+        <v>6.319227025</v>
       </c>
       <c r="Q14">
-        <v>6.4796711</v>
+        <v>6.449227025</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.105868090946708</v>
+        <v>0.1064019346273577</v>
       </c>
       <c r="T14">
-        <v>0.5809043484390878</v>
+        <v>0.5860670248382975</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.38069750298977</v>
+        <v>16.96679769506748</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09747393312580122</v>
+        <v>0.09725694621849941</v>
       </c>
       <c r="C15">
-        <v>98.28324078660974</v>
+        <v>97.92459557396018</v>
       </c>
       <c r="D15">
-        <v>106.3242407866097</v>
+        <v>106.7725955739602</v>
       </c>
       <c r="E15">
-        <v>-30.609</v>
+        <v>-29.802</v>
       </c>
       <c r="F15">
-        <v>10.491</v>
+        <v>11.298</v>
       </c>
       <c r="G15">
         <v>2.45</v>
@@ -2511,28 +2511,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M15">
-        <v>0.5276973</v>
+        <v>0.5682894000000001</v>
       </c>
       <c r="N15">
-        <v>8.425636033333333</v>
+        <v>8.385043933333334</v>
       </c>
       <c r="O15">
-        <v>2.106409008333333</v>
+        <v>2.096260983333333</v>
       </c>
       <c r="P15">
-        <v>6.319227025</v>
+        <v>6.28878295</v>
       </c>
       <c r="Q15">
-        <v>6.449227025</v>
+        <v>6.41878295</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1064019346273577</v>
+        <v>0.1069481932773249</v>
       </c>
       <c r="T15">
-        <v>0.5860670248382975</v>
+        <v>0.5913497634793494</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.96679769506748</v>
+        <v>15.75488357399123</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09725694621849941</v>
+        <v>0.0970399593111976</v>
       </c>
       <c r="C16">
-        <v>97.92459557396018</v>
+        <v>97.56974767574995</v>
       </c>
       <c r="D16">
-        <v>106.7725955739602</v>
+        <v>107.22474767575</v>
       </c>
       <c r="E16">
-        <v>-29.802</v>
+        <v>-28.995</v>
       </c>
       <c r="F16">
-        <v>11.298</v>
+        <v>12.105</v>
       </c>
       <c r="G16">
         <v>2.45</v>
@@ -2593,28 +2593,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M16">
-        <v>0.5682894000000001</v>
+        <v>0.6088815000000001</v>
       </c>
       <c r="N16">
-        <v>8.385043933333334</v>
+        <v>8.344451833333332</v>
       </c>
       <c r="O16">
-        <v>2.096260983333333</v>
+        <v>2.086112958333333</v>
       </c>
       <c r="P16">
-        <v>6.28878295</v>
+        <v>6.258338875</v>
       </c>
       <c r="Q16">
-        <v>6.41878295</v>
+        <v>6.388338875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1069481932773249</v>
+        <v>0.1075073050719972</v>
       </c>
       <c r="T16">
-        <v>0.5913497634793494</v>
+        <v>0.596756801853132</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.75488357399123</v>
+        <v>14.70455800239181</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0970399593111976</v>
+        <v>0.0968229724038958</v>
       </c>
       <c r="C17">
-        <v>97.56974767574995</v>
+        <v>97.21874553883409</v>
       </c>
       <c r="D17">
-        <v>107.22474767575</v>
+        <v>107.6807455388341</v>
       </c>
       <c r="E17">
-        <v>-28.995</v>
+        <v>-28.188</v>
       </c>
       <c r="F17">
-        <v>12.105</v>
+        <v>12.912</v>
       </c>
       <c r="G17">
         <v>2.45</v>
@@ -2675,28 +2675,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M17">
-        <v>0.6088815</v>
+        <v>0.6494736</v>
       </c>
       <c r="N17">
-        <v>8.344451833333332</v>
+        <v>8.303859733333333</v>
       </c>
       <c r="O17">
-        <v>2.086112958333333</v>
+        <v>2.075964933333333</v>
       </c>
       <c r="P17">
-        <v>6.258338875</v>
+        <v>6.2278948</v>
       </c>
       <c r="Q17">
-        <v>6.388338875</v>
+        <v>6.3578948</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1075073050719972</v>
+        <v>0.1080797290522569</v>
       </c>
       <c r="T17">
-        <v>0.596756801853132</v>
+        <v>0.6022925792358141</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.70455800239182</v>
+        <v>13.78552312724233</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0968229724038958</v>
+        <v>0.09660598549659398</v>
       </c>
       <c r="C18">
-        <v>97.21874553883409</v>
+        <v>96.87163843771293</v>
       </c>
       <c r="D18">
-        <v>107.6807455388341</v>
+        <v>108.1406384377129</v>
       </c>
       <c r="E18">
-        <v>-28.188</v>
+        <v>-27.381</v>
       </c>
       <c r="F18">
-        <v>12.912</v>
+        <v>13.719</v>
       </c>
       <c r="G18">
         <v>2.45</v>
@@ -2757,28 +2757,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M18">
-        <v>0.6494736</v>
+        <v>0.6900657</v>
       </c>
       <c r="N18">
-        <v>8.303859733333333</v>
+        <v>8.263267633333333</v>
       </c>
       <c r="O18">
-        <v>2.075964933333333</v>
+        <v>2.065816908333333</v>
       </c>
       <c r="P18">
-        <v>6.2278948</v>
+        <v>6.197450724999999</v>
       </c>
       <c r="Q18">
-        <v>6.3578948</v>
+        <v>6.327450724999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1080797290522569</v>
+        <v>0.1086659463814385</v>
       </c>
       <c r="T18">
-        <v>0.6022925792358141</v>
+        <v>0.607961748844585</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.78552312724233</v>
+        <v>12.97461000211043</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09660598549659398</v>
+        <v>0.09659149858929217</v>
       </c>
       <c r="C19">
-        <v>96.87163843771293</v>
+        <v>96.09548264290707</v>
       </c>
       <c r="D19">
-        <v>108.1406384377129</v>
+        <v>108.1714826429071</v>
       </c>
       <c r="E19">
-        <v>-27.381</v>
+        <v>-26.574</v>
       </c>
       <c r="F19">
-        <v>13.719</v>
+        <v>14.526</v>
       </c>
       <c r="G19">
         <v>2.45</v>
@@ -2839,45 +2839,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M19">
-        <v>0.6900657</v>
+        <v>0.7524468000000001</v>
       </c>
       <c r="N19">
-        <v>8.263267633333333</v>
+        <v>8.200886533333334</v>
       </c>
       <c r="O19">
-        <v>2.065816908333333</v>
+        <v>2.050221633333333</v>
       </c>
       <c r="P19">
-        <v>6.197450724999999</v>
+        <v>6.150664900000001</v>
       </c>
       <c r="Q19">
-        <v>6.327450724999999</v>
+        <v>6.280664900000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1086659463814385</v>
+        <v>0.1092664616942587</v>
       </c>
       <c r="T19">
-        <v>0.607961748844585</v>
+        <v>0.613769190882838</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.97461000211043</v>
+        <v>11.89895861519158</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09659149858929217</v>
+        <v>0.09638576168199037</v>
       </c>
       <c r="C20">
-        <v>96.09548264290707</v>
+        <v>95.72842593044932</v>
       </c>
       <c r="D20">
-        <v>108.1714826429071</v>
+        <v>108.6114259304493</v>
       </c>
       <c r="E20">
-        <v>-26.574</v>
+        <v>-25.767</v>
       </c>
       <c r="F20">
-        <v>14.526</v>
+        <v>15.333</v>
       </c>
       <c r="G20">
         <v>2.45</v>
@@ -2921,28 +2921,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M20">
-        <v>0.7524468</v>
+        <v>0.7942494</v>
       </c>
       <c r="N20">
-        <v>8.200886533333334</v>
+        <v>8.159083933333333</v>
       </c>
       <c r="O20">
-        <v>2.050221633333333</v>
+        <v>2.039770983333333</v>
       </c>
       <c r="P20">
-        <v>6.150664900000001</v>
+        <v>6.119312949999999</v>
       </c>
       <c r="Q20">
-        <v>6.280664900000001</v>
+        <v>6.249312949999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1092664616942587</v>
+        <v>0.1098818045456671</v>
       </c>
       <c r="T20">
-        <v>0.613769190882838</v>
+        <v>0.6197200265516652</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.89895861519158</v>
+        <v>11.27269763544465</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09638576168199037</v>
+        <v>0.09618002477468857</v>
       </c>
       <c r="C21">
-        <v>95.72842593044932</v>
+        <v>95.36496241080046</v>
       </c>
       <c r="D21">
-        <v>108.6114259304493</v>
+        <v>109.0549624108005</v>
       </c>
       <c r="E21">
-        <v>-25.767</v>
+        <v>-24.96</v>
       </c>
       <c r="F21">
-        <v>15.333</v>
+        <v>16.14</v>
       </c>
       <c r="G21">
         <v>2.45</v>
@@ -3003,28 +3003,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M21">
-        <v>0.7942494</v>
+        <v>0.836052</v>
       </c>
       <c r="N21">
-        <v>8.159083933333333</v>
+        <v>8.117281333333333</v>
       </c>
       <c r="O21">
-        <v>2.039770983333333</v>
+        <v>2.029320333333333</v>
       </c>
       <c r="P21">
-        <v>6.119312949999999</v>
+        <v>6.087961</v>
       </c>
       <c r="Q21">
-        <v>6.249312949999999</v>
+        <v>6.217961</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1098818045456671</v>
+        <v>0.1105125309683607</v>
       </c>
       <c r="T21">
-        <v>0.6197200265516652</v>
+        <v>0.6258196331122131</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.27269763544465</v>
+        <v>10.70906275367242</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09618002477468857</v>
+        <v>0.09597428786738674</v>
       </c>
       <c r="C22">
-        <v>95.36496241080046</v>
+        <v>95.00513628502895</v>
       </c>
       <c r="D22">
-        <v>109.0549624108005</v>
+        <v>109.502136285029</v>
       </c>
       <c r="E22">
-        <v>-24.96</v>
+        <v>-24.153</v>
       </c>
       <c r="F22">
-        <v>16.14</v>
+        <v>16.947</v>
       </c>
       <c r="G22">
         <v>2.45</v>
@@ -3085,28 +3085,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M22">
-        <v>0.836052</v>
+        <v>0.8778546000000002</v>
       </c>
       <c r="N22">
-        <v>8.117281333333333</v>
+        <v>8.075478733333332</v>
       </c>
       <c r="O22">
-        <v>2.029320333333333</v>
+        <v>2.018869683333333</v>
       </c>
       <c r="P22">
-        <v>6.087961</v>
+        <v>6.056609049999999</v>
       </c>
       <c r="Q22">
-        <v>6.217961</v>
+        <v>6.186609049999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1105125309683607</v>
+        <v>0.1111592251485908</v>
       </c>
       <c r="T22">
-        <v>0.6258196331122131</v>
+        <v>0.6320736600920154</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.70906275367242</v>
+        <v>10.19910738444992</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09597428786738674</v>
+        <v>0.09604905096008491</v>
       </c>
       <c r="C23">
-        <v>95.00513628502895</v>
+        <v>94.03521343953622</v>
       </c>
       <c r="D23">
-        <v>109.502136285029</v>
+        <v>109.3392134395362</v>
       </c>
       <c r="E23">
-        <v>-24.153</v>
+        <v>-23.346</v>
       </c>
       <c r="F23">
-        <v>16.947</v>
+        <v>17.754</v>
       </c>
       <c r="G23">
         <v>2.45</v>
@@ -3167,45 +3167,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M23">
-        <v>0.8778545999999999</v>
+        <v>0.9498390000000001</v>
       </c>
       <c r="N23">
-        <v>8.075478733333334</v>
+        <v>8.003494333333332</v>
       </c>
       <c r="O23">
-        <v>2.018869683333333</v>
+        <v>2.000873583333333</v>
       </c>
       <c r="P23">
-        <v>6.05660905</v>
+        <v>6.002620749999999</v>
       </c>
       <c r="Q23">
-        <v>6.18660905</v>
+        <v>6.132620749999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1111592251485908</v>
+        <v>0.1118225012308781</v>
       </c>
       <c r="T23">
-        <v>0.6320736600920154</v>
+        <v>0.6384880467379663</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.19910738444992</v>
+        <v>9.426158889383707</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09604905096008491</v>
+        <v>0.0958560640527831</v>
       </c>
       <c r="C24">
-        <v>94.03521343953622</v>
+        <v>93.64976149865367</v>
       </c>
       <c r="D24">
-        <v>109.3392134395362</v>
+        <v>109.7607614986537</v>
       </c>
       <c r="E24">
-        <v>-23.346</v>
+        <v>-22.539</v>
       </c>
       <c r="F24">
-        <v>17.754</v>
+        <v>18.561</v>
       </c>
       <c r="G24">
         <v>2.45</v>
@@ -3249,28 +3249,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M24">
-        <v>0.9498390000000001</v>
+        <v>0.9930135</v>
       </c>
       <c r="N24">
-        <v>8.003494333333332</v>
+        <v>7.960319833333333</v>
       </c>
       <c r="O24">
-        <v>2.000873583333333</v>
+        <v>1.990079958333333</v>
       </c>
       <c r="P24">
-        <v>6.002620749999999</v>
+        <v>5.970239875</v>
       </c>
       <c r="Q24">
-        <v>6.132620749999999</v>
+        <v>6.100239875</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1118225012308781</v>
+        <v>0.1125030052633547</v>
       </c>
       <c r="T24">
-        <v>0.6384880467379663</v>
+        <v>0.6450690408292669</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.426158889383707</v>
+        <v>9.016325894193113</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0958560640527831</v>
+        <v>0.09566307714548131</v>
       </c>
       <c r="C25">
-        <v>93.64976149865367</v>
+        <v>93.26757262378567</v>
       </c>
       <c r="D25">
-        <v>109.7607614986537</v>
+        <v>110.1855726237857</v>
       </c>
       <c r="E25">
-        <v>-22.539</v>
+        <v>-21.732</v>
       </c>
       <c r="F25">
-        <v>18.561</v>
+        <v>19.368</v>
       </c>
       <c r="G25">
         <v>2.45</v>
@@ -3331,28 +3331,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M25">
-        <v>0.9930135</v>
+        <v>1.036188</v>
       </c>
       <c r="N25">
-        <v>7.960319833333333</v>
+        <v>7.917145333333333</v>
       </c>
       <c r="O25">
-        <v>1.990079958333333</v>
+        <v>1.979286333333333</v>
       </c>
       <c r="P25">
-        <v>5.970239875</v>
+        <v>5.937859</v>
       </c>
       <c r="Q25">
-        <v>6.100239875</v>
+        <v>6.067858999999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1125030052633547</v>
+        <v>0.1132014172966859</v>
       </c>
       <c r="T25">
-        <v>0.6450690408292669</v>
+        <v>0.6518232189756015</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.016325894193113</v>
+        <v>8.640645648601733</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09566307714548131</v>
+        <v>0.09547009023817948</v>
       </c>
       <c r="C26">
-        <v>93.26757262378567</v>
+        <v>92.88868484963379</v>
       </c>
       <c r="D26">
-        <v>110.1855726237857</v>
+        <v>110.6136848496338</v>
       </c>
       <c r="E26">
-        <v>-21.732</v>
+        <v>-20.925</v>
       </c>
       <c r="F26">
-        <v>19.368</v>
+        <v>20.175</v>
       </c>
       <c r="G26">
         <v>2.45</v>
@@ -3413,28 +3413,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M26">
-        <v>1.036188</v>
+        <v>1.0793625</v>
       </c>
       <c r="N26">
-        <v>7.917145333333333</v>
+        <v>7.873970833333333</v>
       </c>
       <c r="O26">
-        <v>1.979286333333333</v>
+        <v>1.968492708333333</v>
       </c>
       <c r="P26">
-        <v>5.937859</v>
+        <v>5.905478125</v>
       </c>
       <c r="Q26">
-        <v>6.067858999999999</v>
+        <v>6.035478125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1132014172966859</v>
+        <v>0.113918453650906</v>
       </c>
       <c r="T26">
-        <v>0.6518232189756015</v>
+        <v>0.6587575085391717</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.640645648601733</v>
+        <v>8.295019822657665</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09547009023817948</v>
+        <v>0.09527710333087766</v>
       </c>
       <c r="C27">
-        <v>92.88868484963379</v>
+        <v>92.51313680432143</v>
       </c>
       <c r="D27">
-        <v>110.6136848496338</v>
+        <v>111.0451368043214</v>
       </c>
       <c r="E27">
-        <v>-20.925</v>
+        <v>-20.118</v>
       </c>
       <c r="F27">
-        <v>20.175</v>
+        <v>20.982</v>
       </c>
       <c r="G27">
         <v>2.45</v>
@@ -3495,28 +3495,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M27">
-        <v>1.0793625</v>
+        <v>1.122537</v>
       </c>
       <c r="N27">
-        <v>7.873970833333333</v>
+        <v>7.830796333333333</v>
       </c>
       <c r="O27">
-        <v>1.968492708333333</v>
+        <v>1.957699083333333</v>
       </c>
       <c r="P27">
-        <v>5.905478125</v>
+        <v>5.87309725</v>
       </c>
       <c r="Q27">
-        <v>6.035478125</v>
+        <v>6.00309725</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.113918453650906</v>
+        <v>0.1146548693660509</v>
       </c>
       <c r="T27">
-        <v>0.6587575085391717</v>
+        <v>0.6658792113341898</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.295019822657665</v>
+        <v>7.975980598709292</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09527710333087766</v>
+        <v>0.09508411642357588</v>
       </c>
       <c r="C28">
-        <v>92.51313680432143</v>
+        <v>92.14096772101243</v>
       </c>
       <c r="D28">
-        <v>111.0451368043214</v>
+        <v>111.4799677210124</v>
       </c>
       <c r="E28">
-        <v>-20.118</v>
+        <v>-19.311</v>
       </c>
       <c r="F28">
-        <v>20.982</v>
+        <v>21.789</v>
       </c>
       <c r="G28">
         <v>2.45</v>
@@ -3577,28 +3577,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M28">
-        <v>1.122537</v>
+        <v>1.1657115</v>
       </c>
       <c r="N28">
-        <v>7.830796333333333</v>
+        <v>7.787621833333333</v>
       </c>
       <c r="O28">
-        <v>1.957699083333333</v>
+        <v>1.946905458333333</v>
       </c>
       <c r="P28">
-        <v>5.87309725</v>
+        <v>5.840716375</v>
       </c>
       <c r="Q28">
-        <v>6.00309725</v>
+        <v>5.970716374999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1146548693660509</v>
+        <v>0.1154114608542135</v>
       </c>
       <c r="T28">
-        <v>0.6658792113341898</v>
+        <v>0.6731960292742769</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.975980598709292</v>
+        <v>7.680573909868207</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09508411642357588</v>
+        <v>0.09505912951627404</v>
       </c>
       <c r="C29">
-        <v>92.14096772101243</v>
+        <v>91.39051641862058</v>
       </c>
       <c r="D29">
-        <v>111.4799677210124</v>
+        <v>111.5365164186206</v>
       </c>
       <c r="E29">
-        <v>-19.311</v>
+        <v>-18.504</v>
       </c>
       <c r="F29">
-        <v>21.789</v>
+        <v>22.596</v>
       </c>
       <c r="G29">
         <v>2.45</v>
@@ -3659,45 +3659,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M29">
-        <v>1.1657115</v>
+        <v>1.2269628</v>
       </c>
       <c r="N29">
-        <v>7.787621833333333</v>
+        <v>7.726370533333333</v>
       </c>
       <c r="O29">
-        <v>1.946905458333333</v>
+        <v>1.931592633333333</v>
       </c>
       <c r="P29">
-        <v>5.840716375</v>
+        <v>5.7947779</v>
       </c>
       <c r="Q29">
-        <v>5.970716374999999</v>
+        <v>5.9247779</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1154114608542135</v>
+        <v>0.1161890687726028</v>
       </c>
       <c r="T29">
-        <v>0.6731960292742769</v>
+        <v>0.6807160921571441</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.680573909868207</v>
+        <v>7.297151415946215</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09505912951627404</v>
+        <v>0.09487214260897223</v>
       </c>
       <c r="C30">
-        <v>91.39051641862058</v>
+        <v>91.00852065009512</v>
       </c>
       <c r="D30">
-        <v>111.5365164186206</v>
+        <v>111.9615206500951</v>
       </c>
       <c r="E30">
-        <v>-18.504</v>
+        <v>-17.697</v>
       </c>
       <c r="F30">
-        <v>22.596</v>
+        <v>23.403</v>
       </c>
       <c r="G30">
         <v>2.45</v>
@@ -3741,28 +3741,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M30">
-        <v>1.2269628</v>
+        <v>1.2707829</v>
       </c>
       <c r="N30">
-        <v>7.726370533333333</v>
+        <v>7.682550433333333</v>
       </c>
       <c r="O30">
-        <v>1.931592633333333</v>
+        <v>1.920637608333333</v>
       </c>
       <c r="P30">
-        <v>5.7947779</v>
+        <v>5.761912825</v>
       </c>
       <c r="Q30">
-        <v>5.9247779</v>
+        <v>5.891912824999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1161890687726028</v>
+        <v>0.1169885811393975</v>
       </c>
       <c r="T30">
-        <v>0.6807160921571441</v>
+        <v>0.6884479877972751</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.297151415946215</v>
+        <v>7.045525505051518</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09487214260897221</v>
+        <v>0.09468515570167041</v>
       </c>
       <c r="C31">
-        <v>91.00852065009516</v>
+        <v>90.62977618457541</v>
       </c>
       <c r="D31">
-        <v>111.9615206500952</v>
+        <v>112.3897761845754</v>
       </c>
       <c r="E31">
-        <v>-17.697</v>
+        <v>-16.89</v>
       </c>
       <c r="F31">
-        <v>23.403</v>
+        <v>24.21</v>
       </c>
       <c r="G31">
         <v>2.45</v>
@@ -3823,28 +3823,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M31">
-        <v>1.2707829</v>
+        <v>1.314603</v>
       </c>
       <c r="N31">
-        <v>7.682550433333333</v>
+        <v>7.638730333333333</v>
       </c>
       <c r="O31">
-        <v>1.920637608333333</v>
+        <v>1.909682583333333</v>
       </c>
       <c r="P31">
-        <v>5.761912825</v>
+        <v>5.729047749999999</v>
       </c>
       <c r="Q31">
-        <v>5.891912824999999</v>
+        <v>5.859047749999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1169885811393975</v>
+        <v>0.117810936716672</v>
       </c>
       <c r="T31">
-        <v>0.6884479877972751</v>
+        <v>0.69640079474141</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.045525505051518</v>
+        <v>6.810674654883135</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09468515570167041</v>
+        <v>0.09449816879436862</v>
       </c>
       <c r="C32">
-        <v>90.62977618457541</v>
+        <v>90.25432047425564</v>
       </c>
       <c r="D32">
-        <v>112.3897761845754</v>
+        <v>112.8213204742556</v>
       </c>
       <c r="E32">
-        <v>-16.89</v>
+        <v>-16.083</v>
       </c>
       <c r="F32">
-        <v>24.21</v>
+        <v>25.017</v>
       </c>
       <c r="G32">
         <v>2.45</v>
@@ -3905,28 +3905,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M32">
-        <v>1.314603</v>
+        <v>1.3584231</v>
       </c>
       <c r="N32">
-        <v>7.638730333333333</v>
+        <v>7.594910233333334</v>
       </c>
       <c r="O32">
-        <v>1.909682583333333</v>
+        <v>1.898727558333333</v>
       </c>
       <c r="P32">
-        <v>5.729047749999999</v>
+        <v>5.696182675</v>
       </c>
       <c r="Q32">
-        <v>5.859047749999999</v>
+        <v>5.826182675</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.117810936716672</v>
+        <v>0.1186571286874908</v>
       </c>
       <c r="T32">
-        <v>0.69640079474141</v>
+        <v>0.7045841178288532</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.810674654883135</v>
+        <v>6.59097547246755</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09449816879436862</v>
+        <v>0.09431118188706679</v>
       </c>
       <c r="C33">
-        <v>90.25432047425564</v>
+        <v>89.88219154876998</v>
       </c>
       <c r="D33">
-        <v>112.8213204742556</v>
+        <v>113.25619154877</v>
       </c>
       <c r="E33">
-        <v>-16.083</v>
+        <v>-15.276</v>
       </c>
       <c r="F33">
-        <v>25.017</v>
+        <v>25.824</v>
       </c>
       <c r="G33">
         <v>2.45</v>
@@ -3987,28 +3987,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M33">
-        <v>1.3584231</v>
+        <v>1.4022432</v>
       </c>
       <c r="N33">
-        <v>7.594910233333334</v>
+        <v>7.551090133333333</v>
       </c>
       <c r="O33">
-        <v>1.898727558333333</v>
+        <v>1.887772533333333</v>
       </c>
       <c r="P33">
-        <v>5.696182675</v>
+        <v>5.6633176</v>
       </c>
       <c r="Q33">
-        <v>5.826182675</v>
+        <v>5.7933176</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1186571286874908</v>
+        <v>0.1195282086574512</v>
       </c>
       <c r="T33">
-        <v>0.7045841178288532</v>
+        <v>0.7130081268894565</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.59097547246755</v>
+        <v>6.385007488952938</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09431118188706679</v>
+        <v>0.09412419497976499</v>
       </c>
       <c r="C34">
-        <v>89.88219154876998</v>
+        <v>89.51342802636371</v>
       </c>
       <c r="D34">
-        <v>113.25619154877</v>
+        <v>113.6944280263637</v>
       </c>
       <c r="E34">
-        <v>-15.276</v>
+        <v>-14.469</v>
       </c>
       <c r="F34">
-        <v>25.824</v>
+        <v>26.631</v>
       </c>
       <c r="G34">
         <v>2.45</v>
@@ -4069,28 +4069,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M34">
-        <v>1.4022432</v>
+        <v>1.4460633</v>
       </c>
       <c r="N34">
-        <v>7.551090133333333</v>
+        <v>7.507270033333333</v>
       </c>
       <c r="O34">
-        <v>1.887772533333333</v>
+        <v>1.876817508333333</v>
       </c>
       <c r="P34">
-        <v>5.6633176</v>
+        <v>5.630452524999999</v>
       </c>
       <c r="Q34">
-        <v>5.7933176</v>
+        <v>5.760452524999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1195282086574512</v>
+        <v>0.1204252910145746</v>
       </c>
       <c r="T34">
-        <v>0.7130081268894565</v>
+        <v>0.7216835989070927</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.385007488952938</v>
+        <v>6.191522413530121</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09412419497976499</v>
+        <v>0.09419220807246317</v>
       </c>
       <c r="C35">
-        <v>89.51342802636371</v>
+        <v>88.54663557256526</v>
       </c>
       <c r="D35">
-        <v>113.6944280263637</v>
+        <v>113.5346355725653</v>
       </c>
       <c r="E35">
-        <v>-14.469</v>
+        <v>-13.662</v>
       </c>
       <c r="F35">
-        <v>26.631</v>
+        <v>27.438</v>
       </c>
       <c r="G35">
         <v>2.45</v>
@@ -4151,45 +4151,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M35">
-        <v>1.4460633</v>
+        <v>1.5173214</v>
       </c>
       <c r="N35">
-        <v>7.507270033333333</v>
+        <v>7.436011933333333</v>
       </c>
       <c r="O35">
-        <v>1.876817508333333</v>
+        <v>1.859002983333333</v>
       </c>
       <c r="P35">
-        <v>5.630452524999999</v>
+        <v>5.57700895</v>
       </c>
       <c r="Q35">
-        <v>5.760452524999999</v>
+        <v>5.70700895</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1204252910145746</v>
+        <v>0.1213495576855503</v>
       </c>
       <c r="T35">
-        <v>0.7216835989070927</v>
+        <v>0.7306219640161723</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.191522413530121</v>
+        <v>5.900749395173186</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09419220807246317</v>
+        <v>0.09401272116516135</v>
       </c>
       <c r="C36">
-        <v>88.54663557256526</v>
+        <v>88.16230370077048</v>
       </c>
       <c r="D36">
-        <v>113.5346355725653</v>
+        <v>113.9573037007705</v>
       </c>
       <c r="E36">
-        <v>-13.662</v>
+        <v>-12.855</v>
       </c>
       <c r="F36">
-        <v>27.438</v>
+        <v>28.245</v>
       </c>
       <c r="G36">
         <v>2.45</v>
@@ -4233,28 +4233,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M36">
-        <v>1.5173214</v>
+        <v>1.5619485</v>
       </c>
       <c r="N36">
-        <v>7.436011933333333</v>
+        <v>7.391384833333333</v>
       </c>
       <c r="O36">
-        <v>1.859002983333333</v>
+        <v>1.847846208333333</v>
       </c>
       <c r="P36">
-        <v>5.57700895</v>
+        <v>5.543538624999999</v>
       </c>
       <c r="Q36">
-        <v>5.70700895</v>
+        <v>5.673538624999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1213495576855503</v>
+        <v>0.1223022633310175</v>
       </c>
       <c r="T36">
-        <v>0.7306219640161723</v>
+        <v>0.7398353557439928</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.900749395173186</v>
+        <v>5.732156555311094</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09401272116516135</v>
+        <v>0.09383323425785955</v>
       </c>
       <c r="C37">
-        <v>88.16230370077048</v>
+        <v>87.7811306166908</v>
       </c>
       <c r="D37">
-        <v>113.9573037007705</v>
+        <v>114.3831306166908</v>
       </c>
       <c r="E37">
-        <v>-12.855</v>
+        <v>-12.048</v>
       </c>
       <c r="F37">
-        <v>28.245</v>
+        <v>29.052</v>
       </c>
       <c r="G37">
         <v>2.45</v>
@@ -4315,28 +4315,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M37">
-        <v>1.5619485</v>
+        <v>1.6065756</v>
       </c>
       <c r="N37">
-        <v>7.391384833333333</v>
+        <v>7.346757733333333</v>
       </c>
       <c r="O37">
-        <v>1.847846208333333</v>
+        <v>1.836689433333333</v>
       </c>
       <c r="P37">
-        <v>5.543538624999999</v>
+        <v>5.510068299999999</v>
       </c>
       <c r="Q37">
-        <v>5.673538624999999</v>
+        <v>5.640068299999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1223022633310175</v>
+        <v>0.1232847410279056</v>
       </c>
       <c r="T37">
-        <v>0.7398353557439928</v>
+        <v>0.7493366659633078</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.732156555311094</v>
+        <v>5.572929984330231</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09383323425785957</v>
+        <v>0.09365374735055773</v>
       </c>
       <c r="C38">
-        <v>87.78113061669077</v>
+        <v>87.40315186368937</v>
       </c>
       <c r="D38">
-        <v>114.3831306166908</v>
+        <v>114.8121518636894</v>
       </c>
       <c r="E38">
-        <v>-12.048</v>
+        <v>-11.241</v>
       </c>
       <c r="F38">
-        <v>29.052</v>
+        <v>29.859</v>
       </c>
       <c r="G38">
         <v>2.45</v>
@@ -4397,28 +4397,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M38">
-        <v>1.6065756</v>
+        <v>1.6512027</v>
       </c>
       <c r="N38">
-        <v>7.346757733333333</v>
+        <v>7.302130633333332</v>
       </c>
       <c r="O38">
-        <v>1.836689433333333</v>
+        <v>1.825532658333333</v>
       </c>
       <c r="P38">
-        <v>5.510068299999999</v>
+        <v>5.476597974999999</v>
       </c>
       <c r="Q38">
-        <v>5.640068299999999</v>
+        <v>5.606597974999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1232847410279056</v>
+        <v>0.1242984084929488</v>
       </c>
       <c r="T38">
-        <v>0.7493366659633078</v>
+        <v>0.759139605078474</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.572929984330232</v>
+        <v>5.422310255024009</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09365374735055773</v>
+        <v>0.09347426044325594</v>
       </c>
       <c r="C39">
-        <v>87.40315186368937</v>
+        <v>87.02840352039217</v>
       </c>
       <c r="D39">
-        <v>114.8121518636894</v>
+        <v>115.2444035203922</v>
       </c>
       <c r="E39">
-        <v>-11.241</v>
+        <v>-10.434</v>
       </c>
       <c r="F39">
-        <v>29.859</v>
+        <v>30.666</v>
       </c>
       <c r="G39">
         <v>2.45</v>
@@ -4479,28 +4479,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M39">
-        <v>1.6512027</v>
+        <v>1.6958298</v>
       </c>
       <c r="N39">
-        <v>7.302130633333332</v>
+        <v>7.257503533333333</v>
       </c>
       <c r="O39">
-        <v>1.825532658333333</v>
+        <v>1.814375883333333</v>
       </c>
       <c r="P39">
-        <v>5.476597974999999</v>
+        <v>5.443127649999999</v>
       </c>
       <c r="Q39">
-        <v>5.606597974999999</v>
+        <v>5.573127649999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1242984084929488</v>
+        <v>0.1253447749084773</v>
       </c>
       <c r="T39">
-        <v>0.759139605078474</v>
+        <v>0.7692587680360651</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.422310255024009</v>
+        <v>5.279617879891799</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09347426044325594</v>
+        <v>0.09329477353595411</v>
       </c>
       <c r="C40">
-        <v>87.02840352039217</v>
+        <v>86.65692221080259</v>
       </c>
       <c r="D40">
-        <v>115.2444035203922</v>
+        <v>115.6799222108026</v>
       </c>
       <c r="E40">
-        <v>-10.434</v>
+        <v>-9.626999999999999</v>
       </c>
       <c r="F40">
-        <v>30.666</v>
+        <v>31.473</v>
       </c>
       <c r="G40">
         <v>2.45</v>
@@ -4561,28 +4561,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M40">
-        <v>1.6958298</v>
+        <v>1.7404569</v>
       </c>
       <c r="N40">
-        <v>7.257503533333333</v>
+        <v>7.212876433333333</v>
       </c>
       <c r="O40">
-        <v>1.814375883333333</v>
+        <v>1.803219108333333</v>
       </c>
       <c r="P40">
-        <v>5.443127649999999</v>
+        <v>5.409657325</v>
       </c>
       <c r="Q40">
-        <v>5.573127649999999</v>
+        <v>5.539657324999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1253447749084773</v>
+        <v>0.1264254484195969</v>
       </c>
       <c r="T40">
-        <v>0.7692587680360651</v>
+        <v>0.7797097068283311</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.279617879891799</v>
+        <v>5.144243062458675</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09329477353595411</v>
+        <v>0.09311528662865232</v>
       </c>
       <c r="C41">
-        <v>86.65692221080259</v>
+        <v>86.28874511464518</v>
       </c>
       <c r="D41">
-        <v>115.6799222108026</v>
+        <v>116.1187451146452</v>
       </c>
       <c r="E41">
-        <v>-9.626999999999999</v>
+        <v>-8.82</v>
       </c>
       <c r="F41">
-        <v>31.473</v>
+        <v>32.28</v>
       </c>
       <c r="G41">
         <v>2.45</v>
@@ -4643,28 +4643,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M41">
-        <v>1.7404569</v>
+        <v>1.785084</v>
       </c>
       <c r="N41">
-        <v>7.212876433333333</v>
+        <v>7.168249333333333</v>
       </c>
       <c r="O41">
-        <v>1.803219108333333</v>
+        <v>1.792062333333333</v>
       </c>
       <c r="P41">
-        <v>5.409657325</v>
+        <v>5.376187</v>
       </c>
       <c r="Q41">
-        <v>5.539657324999999</v>
+        <v>5.506187</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1264254484195969</v>
+        <v>0.1275421443810872</v>
       </c>
       <c r="T41">
-        <v>0.7797097068283311</v>
+        <v>0.790509010247006</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.144243062458675</v>
+        <v>5.015636985897208</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09311528662865232</v>
+        <v>0.09293579972135049</v>
       </c>
       <c r="C42">
-        <v>86.28874511464518</v>
+        <v>85.92390997794664</v>
       </c>
       <c r="D42">
-        <v>116.1187451146452</v>
+        <v>116.5609099779466</v>
       </c>
       <c r="E42">
-        <v>-8.82</v>
+        <v>-8.012999999999998</v>
       </c>
       <c r="F42">
-        <v>32.28</v>
+        <v>33.087</v>
       </c>
       <c r="G42">
         <v>2.45</v>
@@ -4725,28 +4725,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M42">
-        <v>1.785084</v>
+        <v>1.8297111</v>
       </c>
       <c r="N42">
-        <v>7.168249333333333</v>
+        <v>7.123622233333333</v>
       </c>
       <c r="O42">
-        <v>1.792062333333333</v>
+        <v>1.780905558333333</v>
       </c>
       <c r="P42">
-        <v>5.376187</v>
+        <v>5.342716675</v>
       </c>
       <c r="Q42">
-        <v>5.506187</v>
+        <v>5.472716675</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1275421443810872</v>
+        <v>0.1286966944429669</v>
       </c>
       <c r="T42">
-        <v>0.790509010247006</v>
+        <v>0.8016743917476701</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.015636985897208</v>
+        <v>4.893304376485082</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09293579972135049</v>
+        <v>0.09275631281404868</v>
       </c>
       <c r="C43">
-        <v>85.92390997794664</v>
+        <v>85.56245512385867</v>
       </c>
       <c r="D43">
-        <v>116.5609099779466</v>
+        <v>117.0064551238587</v>
       </c>
       <c r="E43">
-        <v>-8.012999999999998</v>
+        <v>-7.205999999999996</v>
       </c>
       <c r="F43">
-        <v>33.087</v>
+        <v>33.89400000000001</v>
       </c>
       <c r="G43">
         <v>2.45</v>
@@ -4807,28 +4807,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M43">
-        <v>1.8297111</v>
+        <v>1.8743382</v>
       </c>
       <c r="N43">
-        <v>7.123622233333333</v>
+        <v>7.078995133333333</v>
       </c>
       <c r="O43">
-        <v>1.780905558333333</v>
+        <v>1.769748783333333</v>
       </c>
       <c r="P43">
-        <v>5.342716675</v>
+        <v>5.30924635</v>
       </c>
       <c r="Q43">
-        <v>5.472716675</v>
+        <v>5.439246349999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1286966944429669</v>
+        <v>0.129891056575946</v>
       </c>
       <c r="T43">
-        <v>0.8016743917476701</v>
+        <v>0.8132247864035292</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.893304376485082</v>
+        <v>4.776797129425912</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0927563128140487</v>
+        <v>0.09257682590674686</v>
       </c>
       <c r="C44">
-        <v>85.56245512385863</v>
+        <v>85.20441946373069</v>
       </c>
       <c r="D44">
-        <v>117.0064551238586</v>
+        <v>117.4554194637307</v>
       </c>
       <c r="E44">
-        <v>-7.206000000000003</v>
+        <v>-6.399000000000001</v>
       </c>
       <c r="F44">
-        <v>33.894</v>
+        <v>34.701</v>
       </c>
       <c r="G44">
         <v>2.45</v>
@@ -4889,28 +4889,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M44">
-        <v>1.8743382</v>
+        <v>1.9189653</v>
       </c>
       <c r="N44">
-        <v>7.078995133333333</v>
+        <v>7.034368033333333</v>
       </c>
       <c r="O44">
-        <v>1.769748783333333</v>
+        <v>1.758592008333333</v>
       </c>
       <c r="P44">
-        <v>5.30924635</v>
+        <v>5.275776025</v>
       </c>
       <c r="Q44">
-        <v>5.439246349999999</v>
+        <v>5.405776025</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.129891056575946</v>
+        <v>0.1311273261521875</v>
       </c>
       <c r="T44">
-        <v>0.8132247864035292</v>
+        <v>0.8251804580648571</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.776797129425914</v>
+        <v>4.665708824090427</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09257682590674686</v>
+        <v>0.09239733899944508</v>
       </c>
       <c r="C45">
-        <v>85.20441946373069</v>
+        <v>84.8498425084378</v>
       </c>
       <c r="D45">
-        <v>117.4554194637307</v>
+        <v>117.9078425084378</v>
       </c>
       <c r="E45">
-        <v>-6.399000000000001</v>
+        <v>-5.591999999999999</v>
       </c>
       <c r="F45">
-        <v>34.701</v>
+        <v>35.508</v>
       </c>
       <c r="G45">
         <v>2.45</v>
@@ -4971,28 +4971,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M45">
-        <v>1.9189653</v>
+        <v>1.9635924</v>
       </c>
       <c r="N45">
-        <v>7.034368033333333</v>
+        <v>6.989740933333333</v>
       </c>
       <c r="O45">
-        <v>1.758592008333333</v>
+        <v>1.747435233333333</v>
       </c>
       <c r="P45">
-        <v>5.275776025</v>
+        <v>5.242305699999999</v>
       </c>
       <c r="Q45">
-        <v>5.405776025</v>
+        <v>5.372305699999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1311273261521875</v>
+        <v>0.1324077482132948</v>
       </c>
       <c r="T45">
-        <v>0.8251804580648571</v>
+        <v>0.8375631179998041</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.665708824090427</v>
+        <v>4.55966998717928</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09239733899944508</v>
+        <v>0.09306160209214326</v>
       </c>
       <c r="C46">
-        <v>84.8498425084378</v>
+        <v>82.38564460039134</v>
       </c>
       <c r="D46">
-        <v>117.9078425084378</v>
+        <v>116.2506446003913</v>
       </c>
       <c r="E46">
-        <v>-5.591999999999999</v>
+        <v>-4.784999999999997</v>
       </c>
       <c r="F46">
-        <v>35.508</v>
+        <v>36.315</v>
       </c>
       <c r="G46">
         <v>2.45</v>
@@ -5053,45 +5053,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M46">
-        <v>1.9635924</v>
+        <v>2.099007</v>
       </c>
       <c r="N46">
-        <v>6.989740933333333</v>
+        <v>6.854326333333333</v>
       </c>
       <c r="O46">
-        <v>1.747435233333333</v>
+        <v>1.713581583333333</v>
       </c>
       <c r="P46">
-        <v>5.242305699999999</v>
+        <v>5.14074475</v>
       </c>
       <c r="Q46">
-        <v>5.372305699999999</v>
+        <v>5.27074475</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1324077482132948</v>
+        <v>0.1337347310766241</v>
       </c>
       <c r="T46">
-        <v>0.8375631179998041</v>
+        <v>0.8503960564778398</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.55966998717928</v>
+        <v>4.265509039909506</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09306160209214326</v>
+        <v>0.09290086518484143</v>
       </c>
       <c r="C47">
-        <v>82.38564460039134</v>
+        <v>81.97536277131198</v>
       </c>
       <c r="D47">
-        <v>116.2506446003913</v>
+        <v>116.647362771312</v>
       </c>
       <c r="E47">
-        <v>-4.784999999999997</v>
+        <v>-3.978000000000002</v>
       </c>
       <c r="F47">
-        <v>36.315</v>
+        <v>37.122</v>
       </c>
       <c r="G47">
         <v>2.45</v>
@@ -5135,28 +5135,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M47">
-        <v>2.099007</v>
+        <v>2.1456516</v>
       </c>
       <c r="N47">
-        <v>6.854326333333333</v>
+        <v>6.807681733333332</v>
       </c>
       <c r="O47">
-        <v>1.713581583333333</v>
+        <v>1.701920433333333</v>
       </c>
       <c r="P47">
-        <v>5.14074475</v>
+        <v>5.105761299999999</v>
       </c>
       <c r="Q47">
-        <v>5.27074475</v>
+        <v>5.235761299999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1337347310766241</v>
+        <v>0.1351108614534101</v>
       </c>
       <c r="T47">
-        <v>0.8503960564778398</v>
+        <v>0.8637042889735806</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.265509039909506</v>
+        <v>4.172780582520168</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09290086518484143</v>
+        <v>0.09274012827753962</v>
       </c>
       <c r="C48">
-        <v>81.97536277131198</v>
+        <v>81.56779790335752</v>
       </c>
       <c r="D48">
-        <v>116.647362771312</v>
+        <v>117.0467979033575</v>
       </c>
       <c r="E48">
-        <v>-3.978000000000002</v>
+        <v>-3.170999999999999</v>
       </c>
       <c r="F48">
-        <v>37.122</v>
+        <v>37.929</v>
       </c>
       <c r="G48">
         <v>2.45</v>
@@ -5217,28 +5217,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M48">
-        <v>2.1456516</v>
+        <v>2.1922962</v>
       </c>
       <c r="N48">
-        <v>6.807681733333332</v>
+        <v>6.761037133333333</v>
       </c>
       <c r="O48">
-        <v>1.701920433333333</v>
+        <v>1.690259283333333</v>
       </c>
       <c r="P48">
-        <v>5.105761299999999</v>
+        <v>5.07077785</v>
       </c>
       <c r="Q48">
-        <v>5.235761299999999</v>
+        <v>5.20077785</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1351108614534101</v>
+        <v>0.1365389212783766</v>
       </c>
       <c r="T48">
-        <v>0.8637042889735806</v>
+        <v>0.877514718921991</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.172780582520168</v>
+        <v>4.083998016934633</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09274012827753962</v>
+        <v>0.09383939137023782</v>
       </c>
       <c r="C49">
-        <v>81.56779790335752</v>
+        <v>78.08247036040328</v>
       </c>
       <c r="D49">
-        <v>117.0467979033575</v>
+        <v>114.3684703604033</v>
       </c>
       <c r="E49">
-        <v>-3.170999999999999</v>
+        <v>-2.363999999999997</v>
       </c>
       <c r="F49">
-        <v>37.929</v>
+        <v>38.736</v>
       </c>
       <c r="G49">
         <v>2.45</v>
@@ -5299,45 +5299,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M49">
-        <v>2.1922962</v>
+        <v>2.3745168</v>
       </c>
       <c r="N49">
-        <v>6.761037133333333</v>
+        <v>6.578816533333333</v>
       </c>
       <c r="O49">
-        <v>1.690259283333333</v>
+        <v>1.644704133333333</v>
       </c>
       <c r="P49">
-        <v>5.07077785</v>
+        <v>4.9341124</v>
       </c>
       <c r="Q49">
-        <v>5.20077785</v>
+        <v>5.0641124</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1365389212783766</v>
+        <v>0.1380219064812266</v>
       </c>
       <c r="T49">
-        <v>0.877514718921991</v>
+        <v>0.8918563192530324</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.083998016934633</v>
+        <v>3.770591698207118</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09383939137023782</v>
+        <v>0.093704904462936</v>
       </c>
       <c r="C50">
-        <v>78.08247036040328</v>
+        <v>77.59654524916567</v>
       </c>
       <c r="D50">
-        <v>114.3684703604033</v>
+        <v>114.6895452491657</v>
       </c>
       <c r="E50">
-        <v>-2.364000000000004</v>
+        <v>-1.557000000000002</v>
       </c>
       <c r="F50">
-        <v>38.736</v>
+        <v>39.543</v>
       </c>
       <c r="G50">
         <v>2.45</v>
@@ -5381,28 +5381,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M50">
-        <v>2.3745168</v>
+        <v>2.4239859</v>
       </c>
       <c r="N50">
-        <v>6.578816533333333</v>
+        <v>6.529347433333333</v>
       </c>
       <c r="O50">
-        <v>1.644704133333333</v>
+        <v>1.632336858333333</v>
       </c>
       <c r="P50">
-        <v>4.9341124</v>
+        <v>4.897010574999999</v>
       </c>
       <c r="Q50">
-        <v>5.0641124</v>
+        <v>5.027010574999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1380219064812266</v>
+        <v>0.1395630479665412</v>
       </c>
       <c r="T50">
-        <v>0.8918563192530324</v>
+        <v>0.9067603352833304</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.770591698207119</v>
+        <v>3.6936408472233</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.093704904462936</v>
+        <v>0.09357041755563419</v>
       </c>
       <c r="C51">
-        <v>77.59654524916567</v>
+        <v>77.1124279667481</v>
       </c>
       <c r="D51">
-        <v>114.6895452491657</v>
+        <v>115.0124279667481</v>
       </c>
       <c r="E51">
-        <v>-1.557000000000002</v>
+        <v>-0.75</v>
       </c>
       <c r="F51">
-        <v>39.543</v>
+        <v>40.35</v>
       </c>
       <c r="G51">
         <v>2.45</v>
@@ -5463,28 +5463,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M51">
-        <v>2.4239859</v>
+        <v>2.473455</v>
       </c>
       <c r="N51">
-        <v>6.529347433333333</v>
+        <v>6.479878333333334</v>
       </c>
       <c r="O51">
-        <v>1.632336858333333</v>
+        <v>1.619969583333333</v>
       </c>
       <c r="P51">
-        <v>4.897010574999999</v>
+        <v>4.859908750000001</v>
       </c>
       <c r="Q51">
-        <v>5.027010574999999</v>
+        <v>4.989908750000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1395630479665412</v>
+        <v>0.1411658351112684</v>
       </c>
       <c r="T51">
-        <v>0.9067603352833304</v>
+        <v>0.9222605119548404</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.6936408472233</v>
+        <v>3.619768030278834</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09357041755563419</v>
+        <v>0.09343593064833237</v>
       </c>
       <c r="C52">
-        <v>77.1124279667481</v>
+        <v>76.63013382486832</v>
       </c>
       <c r="D52">
-        <v>115.0124279667481</v>
+        <v>115.3371338248683</v>
       </c>
       <c r="E52">
-        <v>-0.75</v>
+        <v>0.05700000000000216</v>
       </c>
       <c r="F52">
-        <v>40.35</v>
+        <v>41.157</v>
       </c>
       <c r="G52">
         <v>2.45</v>
@@ -5545,28 +5545,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M52">
-        <v>2.473455</v>
+        <v>2.5229241</v>
       </c>
       <c r="N52">
-        <v>6.479878333333334</v>
+        <v>6.430409233333332</v>
       </c>
       <c r="O52">
-        <v>1.619969583333333</v>
+        <v>1.607602308333333</v>
       </c>
       <c r="P52">
-        <v>4.859908750000001</v>
+        <v>4.822806924999999</v>
       </c>
       <c r="Q52">
-        <v>4.989908750000001</v>
+        <v>4.952806924999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1411658351112684</v>
+        <v>0.1428340421394538</v>
       </c>
       <c r="T52">
-        <v>0.9222605119548404</v>
+        <v>0.9383933488986569</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.619768030278834</v>
+        <v>3.548792186547876</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09343593064833237</v>
+        <v>0.09439344374103056</v>
       </c>
       <c r="C53">
-        <v>76.63013382486832</v>
+        <v>73.55046477304833</v>
       </c>
       <c r="D53">
-        <v>115.3371338248683</v>
+        <v>113.0644647730483</v>
       </c>
       <c r="E53">
-        <v>0.05700000000000216</v>
+        <v>0.8640000000000043</v>
       </c>
       <c r="F53">
-        <v>41.157</v>
+        <v>41.96400000000001</v>
       </c>
       <c r="G53">
         <v>2.45</v>
@@ -5627,45 +5627,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M53">
-        <v>2.5229241</v>
+        <v>2.689892400000001</v>
       </c>
       <c r="N53">
-        <v>6.430409233333332</v>
+        <v>6.263440933333333</v>
       </c>
       <c r="O53">
-        <v>1.607602308333333</v>
+        <v>1.565860233333333</v>
       </c>
       <c r="P53">
-        <v>4.822806924999999</v>
+        <v>4.6975807</v>
       </c>
       <c r="Q53">
-        <v>4.952806924999999</v>
+        <v>4.8275807</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1428340421394538</v>
+        <v>0.1445717577938137</v>
       </c>
       <c r="T53">
-        <v>0.9383933488986569</v>
+        <v>0.955198387381799</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.548792186547876</v>
+        <v>3.328509844235156</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09439344374103056</v>
+        <v>0.09427995683372875</v>
       </c>
       <c r="C54">
-        <v>73.55046477304833</v>
+        <v>73.00813778991666</v>
       </c>
       <c r="D54">
-        <v>113.0644647730483</v>
+        <v>113.3291377899167</v>
       </c>
       <c r="E54">
-        <v>0.8640000000000043</v>
+        <v>1.670999999999999</v>
       </c>
       <c r="F54">
-        <v>41.96400000000001</v>
+        <v>42.771</v>
       </c>
       <c r="G54">
         <v>2.45</v>
@@ -5709,28 +5709,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M54">
-        <v>2.689892400000001</v>
+        <v>2.7416211</v>
       </c>
       <c r="N54">
-        <v>6.263440933333333</v>
+        <v>6.211712233333333</v>
       </c>
       <c r="O54">
-        <v>1.565860233333333</v>
+        <v>1.552928058333333</v>
       </c>
       <c r="P54">
-        <v>4.6975807</v>
+        <v>4.658784175</v>
       </c>
       <c r="Q54">
-        <v>4.8275807</v>
+        <v>4.788784175</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1445717577938137</v>
+        <v>0.1463834187951676</v>
       </c>
       <c r="T54">
-        <v>0.955198387381799</v>
+        <v>0.9727185338855004</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.328509844235156</v>
+        <v>3.265707771702418</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09427995683372875</v>
+        <v>0.09416646992642694</v>
       </c>
       <c r="C55">
-        <v>73.00813778991666</v>
+        <v>72.46705286237331</v>
       </c>
       <c r="D55">
-        <v>113.3291377899167</v>
+        <v>113.5950528623733</v>
       </c>
       <c r="E55">
-        <v>1.670999999999999</v>
+        <v>2.478000000000002</v>
       </c>
       <c r="F55">
-        <v>42.771</v>
+        <v>43.578</v>
       </c>
       <c r="G55">
         <v>2.45</v>
@@ -5791,28 +5791,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M55">
-        <v>2.7416211</v>
+        <v>2.793349800000001</v>
       </c>
       <c r="N55">
-        <v>6.211712233333333</v>
+        <v>6.159983533333333</v>
       </c>
       <c r="O55">
-        <v>1.552928058333333</v>
+        <v>1.539995883333333</v>
       </c>
       <c r="P55">
-        <v>4.658784175</v>
+        <v>4.61998765</v>
       </c>
       <c r="Q55">
-        <v>4.788784175</v>
+        <v>4.74998765</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1463834187951676</v>
+        <v>0.1482738476661455</v>
       </c>
       <c r="T55">
-        <v>0.9727185338855004</v>
+        <v>0.9910004258893628</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.265707771702418</v>
+        <v>3.205231701856077</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09416646992642694</v>
+        <v>0.09405298301912512</v>
       </c>
       <c r="C56">
-        <v>72.46705286237331</v>
+        <v>71.92721875404528</v>
       </c>
       <c r="D56">
-        <v>113.5950528623733</v>
+        <v>113.8622187540453</v>
       </c>
       <c r="E56">
-        <v>2.478000000000002</v>
+        <v>3.285000000000004</v>
       </c>
       <c r="F56">
-        <v>43.578</v>
+        <v>44.38500000000001</v>
       </c>
       <c r="G56">
         <v>2.45</v>
@@ -5873,28 +5873,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M56">
-        <v>2.793349800000001</v>
+        <v>2.845078500000001</v>
       </c>
       <c r="N56">
-        <v>6.159983533333333</v>
+        <v>6.108254833333333</v>
       </c>
       <c r="O56">
-        <v>1.539995883333333</v>
+        <v>1.527063708333333</v>
       </c>
       <c r="P56">
-        <v>4.61998765</v>
+        <v>4.581191124999999</v>
       </c>
       <c r="Q56">
-        <v>4.74998765</v>
+        <v>4.711191124999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1482738476661455</v>
+        <v>0.1502482955980559</v>
       </c>
       <c r="T56">
-        <v>0.9910004258893628</v>
+        <v>1.01009484642673</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.205231701856077</v>
+        <v>3.14695476182233</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09405298301912512</v>
+        <v>0.09393949611182331</v>
       </c>
       <c r="C57">
-        <v>71.92721875404528</v>
+        <v>71.38864431119907</v>
       </c>
       <c r="D57">
-        <v>113.8622187540453</v>
+        <v>114.1306443111991</v>
       </c>
       <c r="E57">
-        <v>3.285000000000004</v>
+        <v>4.092000000000006</v>
       </c>
       <c r="F57">
-        <v>44.38500000000001</v>
+        <v>45.19200000000001</v>
       </c>
       <c r="G57">
         <v>2.45</v>
@@ -5955,28 +5955,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M57">
-        <v>2.845078500000001</v>
+        <v>2.8968072</v>
       </c>
       <c r="N57">
-        <v>6.108254833333333</v>
+        <v>6.056526133333333</v>
       </c>
       <c r="O57">
-        <v>1.527063708333333</v>
+        <v>1.514131533333333</v>
       </c>
       <c r="P57">
-        <v>4.581191124999999</v>
+        <v>4.5423946</v>
       </c>
       <c r="Q57">
-        <v>4.711191124999999</v>
+        <v>4.6723946</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1502482955980559</v>
+        <v>0.1523124911632348</v>
       </c>
       <c r="T57">
-        <v>1.01009484642673</v>
+        <v>1.030057195170341</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.14695476182233</v>
+        <v>3.090759141075503</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09393949611182331</v>
+        <v>0.0938260092045215</v>
       </c>
       <c r="C58">
-        <v>71.38864431119907</v>
+        <v>70.8513384637172</v>
       </c>
       <c r="D58">
-        <v>114.1306443111991</v>
+        <v>114.4003384637172</v>
       </c>
       <c r="E58">
-        <v>4.092000000000006</v>
+        <v>4.899000000000008</v>
       </c>
       <c r="F58">
-        <v>45.19200000000001</v>
+        <v>45.99900000000001</v>
       </c>
       <c r="G58">
         <v>2.45</v>
@@ -6037,28 +6037,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M58">
-        <v>2.8968072</v>
+        <v>2.948535900000001</v>
       </c>
       <c r="N58">
-        <v>6.056526133333333</v>
+        <v>6.004797433333332</v>
       </c>
       <c r="O58">
-        <v>1.514131533333333</v>
+        <v>1.501199358333333</v>
       </c>
       <c r="P58">
-        <v>4.5423946</v>
+        <v>4.503598074999999</v>
       </c>
       <c r="Q58">
-        <v>4.6723946</v>
+        <v>4.633598074999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1523124911632348</v>
+        <v>0.1544726958244686</v>
       </c>
       <c r="T58">
-        <v>1.030057195170341</v>
+        <v>1.050948025250865</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.090759141075503</v>
+        <v>3.03653529649523</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0938260092045215</v>
+        <v>0.09710552229721969</v>
       </c>
       <c r="C59">
-        <v>70.8513384637172</v>
+        <v>62.7317258831959</v>
       </c>
       <c r="D59">
-        <v>114.4003384637172</v>
+        <v>107.0877258831959</v>
       </c>
       <c r="E59">
-        <v>4.899000000000008</v>
+        <v>5.706000000000003</v>
       </c>
       <c r="F59">
-        <v>45.99900000000001</v>
+        <v>46.806</v>
       </c>
       <c r="G59">
         <v>2.45</v>
@@ -6119,45 +6119,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M59">
-        <v>2.948535900000001</v>
+        <v>3.365351400000001</v>
       </c>
       <c r="N59">
-        <v>6.004797433333332</v>
+        <v>5.587981933333332</v>
       </c>
       <c r="O59">
-        <v>1.501199358333333</v>
+        <v>1.396995483333333</v>
       </c>
       <c r="P59">
-        <v>4.503598074999999</v>
+        <v>4.19098645</v>
       </c>
       <c r="Q59">
-        <v>4.633598074999999</v>
+        <v>4.320986449999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1544726958244686</v>
+        <v>0.1567357673743326</v>
       </c>
       <c r="T59">
-        <v>1.050948025250865</v>
+        <v>1.072833656763794</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.03653529649523</v>
+        <v>2.660445305454084</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09710552229721969</v>
+        <v>0.09705053538991787</v>
       </c>
       <c r="C60">
-        <v>62.73172588319591</v>
+        <v>62.03962073866428</v>
       </c>
       <c r="D60">
-        <v>107.0877258831959</v>
+        <v>107.2026207386643</v>
       </c>
       <c r="E60">
-        <v>5.705999999999996</v>
+        <v>6.512999999999998</v>
       </c>
       <c r="F60">
-        <v>46.806</v>
+        <v>47.613</v>
       </c>
       <c r="G60">
         <v>2.45</v>
@@ -6201,28 +6201,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M60">
-        <v>3.3653514</v>
+        <v>3.4233747</v>
       </c>
       <c r="N60">
-        <v>5.587981933333333</v>
+        <v>5.529958633333333</v>
       </c>
       <c r="O60">
-        <v>1.396995483333333</v>
+        <v>1.382489658333333</v>
       </c>
       <c r="P60">
-        <v>4.19098645</v>
+        <v>4.147468975</v>
       </c>
       <c r="Q60">
-        <v>4.32098645</v>
+        <v>4.277468975</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1567357673743326</v>
+        <v>0.1591092326583363</v>
       </c>
       <c r="T60">
-        <v>1.072833656763794</v>
+        <v>1.095786880057842</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.660445305454085</v>
+        <v>2.615353012141304</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09705053538991787</v>
+        <v>0.09699554848261607</v>
       </c>
       <c r="C61">
-        <v>62.03962073866428</v>
+        <v>61.34776240124592</v>
       </c>
       <c r="D61">
-        <v>107.2026207386643</v>
+        <v>107.3177624012459</v>
       </c>
       <c r="E61">
-        <v>6.512999999999998</v>
+        <v>7.32</v>
       </c>
       <c r="F61">
-        <v>47.613</v>
+        <v>48.42</v>
       </c>
       <c r="G61">
         <v>2.45</v>
@@ -6283,28 +6283,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M61">
-        <v>3.4233747</v>
+        <v>3.481398</v>
       </c>
       <c r="N61">
-        <v>5.529958633333333</v>
+        <v>5.471935333333333</v>
       </c>
       <c r="O61">
-        <v>1.382489658333333</v>
+        <v>1.367983833333333</v>
       </c>
       <c r="P61">
-        <v>4.147468975</v>
+        <v>4.103951499999999</v>
       </c>
       <c r="Q61">
-        <v>4.277468975</v>
+        <v>4.233951499999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1591092326583363</v>
+        <v>0.1616013712065402</v>
       </c>
       <c r="T61">
-        <v>1.095786880057842</v>
+        <v>1.119887764516592</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.615353012141304</v>
+        <v>2.571763795272282</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09699554848261607</v>
+        <v>0.09694056157531426</v>
       </c>
       <c r="C62">
-        <v>61.34776240124592</v>
+        <v>60.6561516670502</v>
       </c>
       <c r="D62">
-        <v>107.3177624012459</v>
+        <v>107.4331516670502</v>
       </c>
       <c r="E62">
-        <v>7.32</v>
+        <v>8.127000000000002</v>
       </c>
       <c r="F62">
-        <v>48.42</v>
+        <v>49.227</v>
       </c>
       <c r="G62">
         <v>2.45</v>
@@ -6365,28 +6365,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M62">
-        <v>3.481398</v>
+        <v>3.539421300000001</v>
       </c>
       <c r="N62">
-        <v>5.471935333333333</v>
+        <v>5.413912033333332</v>
       </c>
       <c r="O62">
-        <v>1.367983833333333</v>
+        <v>1.353478008333333</v>
       </c>
       <c r="P62">
-        <v>4.103951499999999</v>
+        <v>4.060434024999999</v>
       </c>
       <c r="Q62">
-        <v>4.233951499999999</v>
+        <v>4.190434024999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1616013712065402</v>
+        <v>0.164221311731575</v>
       </c>
       <c r="T62">
-        <v>1.119887764516592</v>
+        <v>1.145224591768099</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.571763795272282</v>
+        <v>2.529603733054703</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09694056157531426</v>
+        <v>0.09869907466801243</v>
       </c>
       <c r="C63">
-        <v>60.6561516670502</v>
+        <v>56.27777343440645</v>
       </c>
       <c r="D63">
-        <v>107.4331516670502</v>
+        <v>103.8617734344064</v>
       </c>
       <c r="E63">
-        <v>8.127000000000002</v>
+        <v>8.933999999999997</v>
       </c>
       <c r="F63">
-        <v>49.227</v>
+        <v>50.034</v>
       </c>
       <c r="G63">
         <v>2.45</v>
@@ -6447,45 +6447,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M63">
-        <v>3.539421300000001</v>
+        <v>3.7925772</v>
       </c>
       <c r="N63">
-        <v>5.413912033333332</v>
+        <v>5.160756133333333</v>
       </c>
       <c r="O63">
-        <v>1.353478008333333</v>
+        <v>1.290189033333333</v>
       </c>
       <c r="P63">
-        <v>4.060434024999999</v>
+        <v>3.8705671</v>
       </c>
       <c r="Q63">
-        <v>4.190434024999999</v>
+        <v>4.0005671</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.164221311731575</v>
+        <v>0.1669791438631906</v>
       </c>
       <c r="T63">
-        <v>1.145224591768099</v>
+        <v>1.171894936243369</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.529603733054703</v>
+        <v>2.360751768832374</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09869907466801243</v>
+        <v>0.09867333776071063</v>
       </c>
       <c r="C64">
-        <v>56.27777343440645</v>
+        <v>55.52132974403798</v>
       </c>
       <c r="D64">
-        <v>103.8617734344064</v>
+        <v>103.912329744038</v>
       </c>
       <c r="E64">
-        <v>8.933999999999997</v>
+        <v>9.741</v>
       </c>
       <c r="F64">
-        <v>50.034</v>
+        <v>50.841</v>
       </c>
       <c r="G64">
         <v>2.45</v>
@@ -6529,28 +6529,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M64">
-        <v>3.7925772</v>
+        <v>3.8537478</v>
       </c>
       <c r="N64">
-        <v>5.160756133333333</v>
+        <v>5.099585533333332</v>
       </c>
       <c r="O64">
-        <v>1.290189033333333</v>
+        <v>1.274896383333333</v>
       </c>
       <c r="P64">
-        <v>3.8705671</v>
+        <v>3.824689149999999</v>
       </c>
       <c r="Q64">
-        <v>4.0005671</v>
+        <v>3.954689149999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1669791438631906</v>
+        <v>0.1698860480019206</v>
       </c>
       <c r="T64">
-        <v>1.171894936243369</v>
+        <v>1.200006920960545</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.360751768832374</v>
+        <v>2.323279518533448</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09867333776071063</v>
+        <v>0.09864760085340882</v>
       </c>
       <c r="C65">
-        <v>55.52132974403798</v>
+        <v>54.76493529575556</v>
       </c>
       <c r="D65">
-        <v>103.912329744038</v>
+        <v>103.9629352957556</v>
       </c>
       <c r="E65">
-        <v>9.741</v>
+        <v>10.548</v>
       </c>
       <c r="F65">
-        <v>50.841</v>
+        <v>51.648</v>
       </c>
       <c r="G65">
         <v>2.45</v>
@@ -6611,28 +6611,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M65">
-        <v>3.8537478</v>
+        <v>3.9149184</v>
       </c>
       <c r="N65">
-        <v>5.099585533333332</v>
+        <v>5.038414933333333</v>
       </c>
       <c r="O65">
-        <v>1.274896383333333</v>
+        <v>1.259603733333333</v>
       </c>
       <c r="P65">
-        <v>3.824689149999999</v>
+        <v>3.7788112</v>
       </c>
       <c r="Q65">
-        <v>3.954689149999999</v>
+        <v>3.9088112</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1698860480019206</v>
+        <v>0.1729544468150245</v>
       </c>
       <c r="T65">
-        <v>1.200006920960545</v>
+        <v>1.229680682606454</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.323279518533448</v>
+        <v>2.286978276056362</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09864760085340882</v>
+        <v>0.09862186394610702</v>
       </c>
       <c r="C66">
-        <v>54.76493529575556</v>
+        <v>54.00859016153728</v>
       </c>
       <c r="D66">
-        <v>103.9629352957556</v>
+        <v>104.0135901615373</v>
       </c>
       <c r="E66">
-        <v>10.548</v>
+        <v>11.355</v>
       </c>
       <c r="F66">
-        <v>51.648</v>
+        <v>52.45500000000001</v>
       </c>
       <c r="G66">
         <v>2.45</v>
@@ -6693,28 +6693,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M66">
-        <v>3.9149184</v>
+        <v>3.976089000000001</v>
       </c>
       <c r="N66">
-        <v>5.038414933333333</v>
+        <v>4.977244333333332</v>
       </c>
       <c r="O66">
-        <v>1.259603733333333</v>
+        <v>1.244311083333333</v>
       </c>
       <c r="P66">
-        <v>3.7788112</v>
+        <v>3.732933249999999</v>
       </c>
       <c r="Q66">
-        <v>3.9088112</v>
+        <v>3.862933249999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1729544468150245</v>
+        <v>0.1761981827031629</v>
       </c>
       <c r="T66">
-        <v>1.229680682606454</v>
+        <v>1.261050087774986</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.286978276056362</v>
+        <v>2.251793994886264</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09862186394610702</v>
+        <v>0.0985961270388052</v>
       </c>
       <c r="C67">
-        <v>54.00859016153728</v>
+        <v>53.25229441350159</v>
       </c>
       <c r="D67">
-        <v>104.0135901615373</v>
+        <v>104.0642944135016</v>
       </c>
       <c r="E67">
-        <v>11.355</v>
+        <v>12.16200000000001</v>
       </c>
       <c r="F67">
-        <v>52.45500000000001</v>
+        <v>53.26200000000001</v>
       </c>
       <c r="G67">
         <v>2.45</v>
@@ -6775,28 +6775,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M67">
-        <v>3.976089000000001</v>
+        <v>4.037259600000001</v>
       </c>
       <c r="N67">
-        <v>4.977244333333332</v>
+        <v>4.916073733333333</v>
       </c>
       <c r="O67">
-        <v>1.244311083333333</v>
+        <v>1.229018433333333</v>
       </c>
       <c r="P67">
-        <v>3.732933249999999</v>
+        <v>3.687055299999999</v>
       </c>
       <c r="Q67">
-        <v>3.862933249999999</v>
+        <v>3.817055299999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1761981827031629</v>
+        <v>0.1796327265847212</v>
       </c>
       <c r="T67">
-        <v>1.261050087774986</v>
+        <v>1.294264752071079</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.251793994886264</v>
+        <v>2.217675904054654</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0985961270388052</v>
+        <v>0.09857039013150339</v>
       </c>
       <c r="C68">
-        <v>53.25229441350159</v>
+        <v>52.49604812390767</v>
       </c>
       <c r="D68">
-        <v>104.0642944135016</v>
+        <v>104.1150481239077</v>
       </c>
       <c r="E68">
-        <v>12.16200000000001</v>
+        <v>12.969</v>
       </c>
       <c r="F68">
-        <v>53.26200000000001</v>
+        <v>54.069</v>
       </c>
       <c r="G68">
         <v>2.45</v>
@@ -6857,28 +6857,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M68">
-        <v>4.037259600000001</v>
+        <v>4.0984302</v>
       </c>
       <c r="N68">
-        <v>4.916073733333333</v>
+        <v>4.854903133333333</v>
       </c>
       <c r="O68">
-        <v>1.229018433333333</v>
+        <v>1.213725783333333</v>
       </c>
       <c r="P68">
-        <v>3.687055299999999</v>
+        <v>3.64117735</v>
       </c>
       <c r="Q68">
-        <v>3.817055299999999</v>
+        <v>3.771177349999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1796327265847212</v>
+        <v>0.1832754246409194</v>
       </c>
       <c r="T68">
-        <v>1.294264752071079</v>
+        <v>1.32949242632451</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.217675904054654</v>
+        <v>2.18457626369563</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09857039013150339</v>
+        <v>0.09854465322420158</v>
       </c>
       <c r="C69">
-        <v>52.49604812390767</v>
+        <v>51.7398513651556</v>
       </c>
       <c r="D69">
-        <v>104.1150481239077</v>
+        <v>104.1658513651556</v>
       </c>
       <c r="E69">
-        <v>12.969</v>
+        <v>13.776</v>
       </c>
       <c r="F69">
-        <v>54.069</v>
+        <v>54.876</v>
       </c>
       <c r="G69">
         <v>2.45</v>
@@ -6939,28 +6939,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M69">
-        <v>4.0984302</v>
+        <v>4.159600800000001</v>
       </c>
       <c r="N69">
-        <v>4.854903133333333</v>
+        <v>4.793732533333332</v>
       </c>
       <c r="O69">
-        <v>1.213725783333333</v>
+        <v>1.198433133333333</v>
       </c>
       <c r="P69">
-        <v>3.64117735</v>
+        <v>3.595299399999999</v>
       </c>
       <c r="Q69">
-        <v>3.771177349999999</v>
+        <v>3.725299399999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1832754246409194</v>
+        <v>0.1871457913256299</v>
       </c>
       <c r="T69">
-        <v>1.32949242632451</v>
+        <v>1.366921830218782</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.18457626369563</v>
+        <v>2.152450142170694</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09854465322420158</v>
+        <v>0.09851891631689977</v>
       </c>
       <c r="C70">
-        <v>51.7398513651556</v>
+        <v>50.98370420978699</v>
       </c>
       <c r="D70">
-        <v>104.1658513651556</v>
+        <v>104.216704209787</v>
       </c>
       <c r="E70">
-        <v>13.776</v>
+        <v>14.58300000000001</v>
       </c>
       <c r="F70">
-        <v>54.876</v>
+        <v>55.68300000000001</v>
       </c>
       <c r="G70">
         <v>2.45</v>
@@ -7021,28 +7021,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M70">
-        <v>4.159600800000001</v>
+        <v>4.220771400000001</v>
       </c>
       <c r="N70">
-        <v>4.793732533333332</v>
+        <v>4.732561933333332</v>
       </c>
       <c r="O70">
-        <v>1.198433133333333</v>
+        <v>1.183140483333333</v>
       </c>
       <c r="P70">
-        <v>3.595299399999999</v>
+        <v>3.549421449999999</v>
       </c>
       <c r="Q70">
-        <v>3.725299399999999</v>
+        <v>3.679421449999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1871457913256299</v>
+        <v>0.1912658590867735</v>
       </c>
       <c r="T70">
-        <v>1.366921830218782</v>
+        <v>1.406766034364296</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.152450142170694</v>
+        <v>2.121255212574017</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09851891631689977</v>
+        <v>0.09849317940959795</v>
       </c>
       <c r="C71">
-        <v>50.98370420978699</v>
+        <v>50.22760673048515</v>
       </c>
       <c r="D71">
-        <v>104.216704209787</v>
+        <v>104.2676067304852</v>
       </c>
       <c r="E71">
-        <v>14.58300000000001</v>
+        <v>15.39000000000001</v>
       </c>
       <c r="F71">
-        <v>55.68300000000001</v>
+        <v>56.49000000000001</v>
       </c>
       <c r="G71">
         <v>2.45</v>
@@ -7103,28 +7103,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M71">
-        <v>4.220771400000001</v>
+        <v>4.281942000000001</v>
       </c>
       <c r="N71">
-        <v>4.732561933333332</v>
+        <v>4.671391333333332</v>
       </c>
       <c r="O71">
-        <v>1.183140483333333</v>
+        <v>1.167847833333333</v>
       </c>
       <c r="P71">
-        <v>3.549421449999999</v>
+        <v>3.503543499999999</v>
       </c>
       <c r="Q71">
-        <v>3.679421449999999</v>
+        <v>3.633543499999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1912658590867735</v>
+        <v>0.1956605980319932</v>
       </c>
       <c r="T71">
-        <v>1.406766034364296</v>
+        <v>1.449266518786178</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.121255212574017</v>
+        <v>2.090951566680102</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09849317940959795</v>
+        <v>0.09846744250229614</v>
       </c>
       <c r="C72">
-        <v>50.22760673048515</v>
+        <v>49.47155900007537</v>
       </c>
       <c r="D72">
-        <v>104.2676067304852</v>
+        <v>104.3185590000754</v>
       </c>
       <c r="E72">
-        <v>15.39000000000001</v>
+        <v>16.19700000000001</v>
       </c>
       <c r="F72">
-        <v>56.49000000000001</v>
+        <v>57.29700000000001</v>
       </c>
       <c r="G72">
         <v>2.45</v>
@@ -7185,28 +7185,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M72">
-        <v>4.281942000000001</v>
+        <v>4.343112600000001</v>
       </c>
       <c r="N72">
-        <v>4.671391333333332</v>
+        <v>4.610220733333332</v>
       </c>
       <c r="O72">
-        <v>1.167847833333333</v>
+        <v>1.152555183333333</v>
       </c>
       <c r="P72">
-        <v>3.503543499999999</v>
+        <v>3.457665549999999</v>
       </c>
       <c r="Q72">
-        <v>3.633543499999999</v>
+        <v>3.587665549999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1956605980319932</v>
+        <v>0.2003584224217109</v>
       </c>
       <c r="T72">
-        <v>1.449266518786178</v>
+        <v>1.494698071099225</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.090951566680102</v>
+        <v>2.061501544614186</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09846744250229615</v>
+        <v>0.09844170559499434</v>
       </c>
       <c r="C73">
-        <v>49.47155900007536</v>
+        <v>48.71556109152543</v>
       </c>
       <c r="D73">
-        <v>104.3185590000754</v>
+        <v>104.3695610915254</v>
       </c>
       <c r="E73">
-        <v>16.197</v>
+        <v>17.004</v>
       </c>
       <c r="F73">
-        <v>57.297</v>
+        <v>58.104</v>
       </c>
       <c r="G73">
         <v>2.45</v>
@@ -7267,28 +7267,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M73">
-        <v>4.3431126</v>
+        <v>4.4042832</v>
       </c>
       <c r="N73">
-        <v>4.610220733333333</v>
+        <v>4.549050133333333</v>
       </c>
       <c r="O73">
-        <v>1.152555183333333</v>
+        <v>1.137262533333333</v>
       </c>
       <c r="P73">
-        <v>3.45766555</v>
+        <v>3.4117876</v>
       </c>
       <c r="Q73">
-        <v>3.58766555</v>
+        <v>3.5417876</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2003584224217108</v>
+        <v>0.2053918056964083</v>
       </c>
       <c r="T73">
-        <v>1.494698071099224</v>
+        <v>1.543374734291774</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.061501544614186</v>
+        <v>2.032869578716767</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09844170559499434</v>
+        <v>0.09841596868769251</v>
       </c>
       <c r="C74">
-        <v>48.71556109152543</v>
+        <v>47.95961307794592</v>
       </c>
       <c r="D74">
-        <v>104.3695610915254</v>
+        <v>104.4206130779459</v>
       </c>
       <c r="E74">
-        <v>17.004</v>
+        <v>17.811</v>
       </c>
       <c r="F74">
-        <v>58.104</v>
+        <v>58.911</v>
       </c>
       <c r="G74">
         <v>2.45</v>
@@ -7349,28 +7349,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M74">
-        <v>4.4042832</v>
+        <v>4.465453800000001</v>
       </c>
       <c r="N74">
-        <v>4.549050133333333</v>
+        <v>4.487879533333333</v>
       </c>
       <c r="O74">
-        <v>1.137262533333333</v>
+        <v>1.121969883333333</v>
       </c>
       <c r="P74">
-        <v>3.4117876</v>
+        <v>3.365909649999999</v>
       </c>
       <c r="Q74">
-        <v>3.5417876</v>
+        <v>3.495909649999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2053918056964083</v>
+        <v>0.2107980321766389</v>
       </c>
       <c r="T74">
-        <v>1.543374734291774</v>
+        <v>1.595657076239327</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.032869578716767</v>
+        <v>2.005022050241195</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09841596868769251</v>
+        <v>0.1062712317803907</v>
       </c>
       <c r="C75">
-        <v>47.95961307794592</v>
+        <v>33.58828895425421</v>
       </c>
       <c r="D75">
-        <v>104.4206130779459</v>
+        <v>90.85628895425421</v>
       </c>
       <c r="E75">
-        <v>17.811</v>
+        <v>18.618</v>
       </c>
       <c r="F75">
-        <v>58.911</v>
+        <v>59.718</v>
       </c>
       <c r="G75">
         <v>2.45</v>
@@ -7431,45 +7431,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M75">
-        <v>4.465453800000001</v>
+        <v>5.37462</v>
       </c>
       <c r="N75">
-        <v>4.487879533333333</v>
+        <v>3.578713333333333</v>
       </c>
       <c r="O75">
-        <v>1.121969883333333</v>
+        <v>0.8946783333333332</v>
       </c>
       <c r="P75">
-        <v>3.365909649999999</v>
+        <v>2.684035</v>
       </c>
       <c r="Q75">
-        <v>3.495909649999999</v>
+        <v>2.814035</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2107980321766389</v>
+        <v>0.2166201222322719</v>
       </c>
       <c r="T75">
-        <v>1.595657076239327</v>
+        <v>1.65196113679823</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.005022050241195</v>
+        <v>1.665854206126821</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1062712317803907</v>
+        <v>0.1063519948730889</v>
       </c>
       <c r="C76">
-        <v>33.58828895425421</v>
+        <v>32.66010657368351</v>
       </c>
       <c r="D76">
-        <v>90.85628895425421</v>
+        <v>90.73510657368351</v>
       </c>
       <c r="E76">
-        <v>18.618</v>
+        <v>19.425</v>
       </c>
       <c r="F76">
-        <v>59.718</v>
+        <v>60.52500000000001</v>
       </c>
       <c r="G76">
         <v>2.45</v>
@@ -7513,28 +7513,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M76">
-        <v>5.37462</v>
+        <v>5.44725</v>
       </c>
       <c r="N76">
-        <v>3.578713333333333</v>
+        <v>3.506083333333333</v>
       </c>
       <c r="O76">
-        <v>0.8946783333333332</v>
+        <v>0.8765208333333332</v>
       </c>
       <c r="P76">
-        <v>2.684035</v>
+        <v>2.6295625</v>
       </c>
       <c r="Q76">
-        <v>2.814035</v>
+        <v>2.759562499999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2166201222322719</v>
+        <v>0.2229079794923556</v>
       </c>
       <c r="T76">
-        <v>1.65196113679823</v>
+        <v>1.712769522201846</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.665854206126821</v>
+        <v>1.643642816711796</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1063519948730889</v>
+        <v>0.1064327579657871</v>
       </c>
       <c r="C77">
-        <v>32.66010657368351</v>
+        <v>31.73224702401027</v>
       </c>
       <c r="D77">
-        <v>90.73510657368351</v>
+        <v>90.61424702401027</v>
       </c>
       <c r="E77">
-        <v>19.425</v>
+        <v>20.232</v>
       </c>
       <c r="F77">
-        <v>60.52500000000001</v>
+        <v>61.332</v>
       </c>
       <c r="G77">
         <v>2.45</v>
@@ -7595,28 +7595,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M77">
-        <v>5.44725</v>
+        <v>5.51988</v>
       </c>
       <c r="N77">
-        <v>3.506083333333333</v>
+        <v>3.433453333333333</v>
       </c>
       <c r="O77">
-        <v>0.8765208333333332</v>
+        <v>0.8583633333333334</v>
       </c>
       <c r="P77">
-        <v>2.6295625</v>
+        <v>2.57509</v>
       </c>
       <c r="Q77">
-        <v>2.759562499999999</v>
+        <v>2.70509</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2229079794923556</v>
+        <v>0.2297198248574462</v>
       </c>
       <c r="T77">
-        <v>1.712769522201846</v>
+        <v>1.778645273055764</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.643642816711796</v>
+        <v>1.622015937544536</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1064327579657871</v>
+        <v>0.1065135210584853</v>
       </c>
       <c r="C78">
-        <v>31.73224702401027</v>
+        <v>30.80470901691418</v>
       </c>
       <c r="D78">
-        <v>90.61424702401027</v>
+        <v>90.49370901691418</v>
       </c>
       <c r="E78">
-        <v>20.232</v>
+        <v>21.039</v>
       </c>
       <c r="F78">
-        <v>61.332</v>
+        <v>62.139</v>
       </c>
       <c r="G78">
         <v>2.45</v>
@@ -7677,28 +7677,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M78">
-        <v>5.51988</v>
+        <v>5.59251</v>
       </c>
       <c r="N78">
-        <v>3.433453333333333</v>
+        <v>3.360823333333333</v>
       </c>
       <c r="O78">
-        <v>0.8583633333333334</v>
+        <v>0.8402058333333333</v>
       </c>
       <c r="P78">
-        <v>2.57509</v>
+        <v>2.5206175</v>
       </c>
       <c r="Q78">
-        <v>2.70509</v>
+        <v>2.6506175</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2297198248574462</v>
+        <v>0.2371240046021099</v>
       </c>
       <c r="T78">
-        <v>1.778645273055764</v>
+        <v>1.850249350070891</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.622015937544536</v>
+        <v>1.600950795498503</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1065135210584853</v>
+        <v>0.1065942841511835</v>
       </c>
       <c r="C79">
-        <v>30.80470901691418</v>
+        <v>29.87749127092082</v>
       </c>
       <c r="D79">
-        <v>90.49370901691418</v>
+        <v>90.37349127092082</v>
       </c>
       <c r="E79">
-        <v>21.039</v>
+        <v>21.846</v>
       </c>
       <c r="F79">
-        <v>62.139</v>
+        <v>62.94600000000001</v>
       </c>
       <c r="G79">
         <v>2.45</v>
@@ -7759,28 +7759,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M79">
-        <v>5.59251</v>
+        <v>5.66514</v>
       </c>
       <c r="N79">
-        <v>3.360823333333333</v>
+        <v>3.288193333333333</v>
       </c>
       <c r="O79">
-        <v>0.8402058333333333</v>
+        <v>0.8220483333333333</v>
       </c>
       <c r="P79">
-        <v>2.5206175</v>
+        <v>2.466145</v>
       </c>
       <c r="Q79">
-        <v>2.6506175</v>
+        <v>2.596145</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2371240046021099</v>
+        <v>0.2452012915962884</v>
       </c>
       <c r="T79">
-        <v>1.850249350070891</v>
+        <v>1.928362888632848</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.600950795498503</v>
+        <v>1.580425785299804</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1065942841511835</v>
+        <v>0.1066750472438817</v>
       </c>
       <c r="C80">
-        <v>29.87749127092082</v>
+        <v>28.95059251135627</v>
       </c>
       <c r="D80">
-        <v>90.37349127092082</v>
+        <v>90.25359251135627</v>
       </c>
       <c r="E80">
-        <v>21.846</v>
+        <v>22.65300000000001</v>
       </c>
       <c r="F80">
-        <v>62.94600000000001</v>
+        <v>63.75300000000001</v>
       </c>
       <c r="G80">
         <v>2.45</v>
@@ -7841,28 +7841,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M80">
-        <v>5.66514</v>
+        <v>5.73777</v>
       </c>
       <c r="N80">
-        <v>3.288193333333333</v>
+        <v>3.215563333333333</v>
       </c>
       <c r="O80">
-        <v>0.8220483333333333</v>
+        <v>0.8038908333333332</v>
       </c>
       <c r="P80">
-        <v>2.466145</v>
+        <v>2.4116725</v>
       </c>
       <c r="Q80">
-        <v>2.596145</v>
+        <v>2.5416725</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2452012915962884</v>
+        <v>0.2540478440184841</v>
       </c>
       <c r="T80">
-        <v>1.928362888632848</v>
+        <v>2.013915811819754</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.580425785299804</v>
+        <v>1.560420395612465</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1066750472438817</v>
+        <v>0.1067558103365798</v>
       </c>
       <c r="C81">
-        <v>28.95059251135627</v>
+        <v>28.0240114703023</v>
       </c>
       <c r="D81">
-        <v>90.25359251135627</v>
+        <v>90.1340114703023</v>
       </c>
       <c r="E81">
-        <v>22.65300000000001</v>
+        <v>23.46</v>
       </c>
       <c r="F81">
-        <v>63.75300000000001</v>
+        <v>64.56</v>
       </c>
       <c r="G81">
         <v>2.45</v>
@@ -7923,28 +7923,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M81">
-        <v>5.73777</v>
+        <v>5.8104</v>
       </c>
       <c r="N81">
-        <v>3.215563333333333</v>
+        <v>3.142933333333334</v>
       </c>
       <c r="O81">
-        <v>0.8038908333333332</v>
+        <v>0.7857333333333334</v>
       </c>
       <c r="P81">
-        <v>2.4116725</v>
+        <v>2.3572</v>
       </c>
       <c r="Q81">
-        <v>2.5416725</v>
+        <v>2.4872</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2540478440184841</v>
+        <v>0.2637790516828992</v>
       </c>
       <c r="T81">
-        <v>2.013915811819754</v>
+        <v>2.10802402732535</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.560420395612465</v>
+        <v>1.540915140667309</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1067558103365798</v>
+        <v>0.106836573429278</v>
       </c>
       <c r="C82">
-        <v>28.0240114703023</v>
+        <v>27.09774688655121</v>
       </c>
       <c r="D82">
-        <v>90.1340114703023</v>
+        <v>90.01474688655121</v>
       </c>
       <c r="E82">
-        <v>23.46</v>
+        <v>24.267</v>
       </c>
       <c r="F82">
-        <v>64.56</v>
+        <v>65.367</v>
       </c>
       <c r="G82">
         <v>2.45</v>
@@ -8005,28 +8005,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M82">
-        <v>5.8104</v>
+        <v>5.88303</v>
       </c>
       <c r="N82">
-        <v>3.142933333333334</v>
+        <v>3.070303333333333</v>
       </c>
       <c r="O82">
-        <v>0.7857333333333334</v>
+        <v>0.7675758333333333</v>
       </c>
       <c r="P82">
-        <v>2.3572</v>
+        <v>2.3027275</v>
       </c>
       <c r="Q82">
-        <v>2.4872</v>
+        <v>2.4327275</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2637790516828992</v>
+        <v>0.2745345969962001</v>
       </c>
       <c r="T82">
-        <v>2.10802402732535</v>
+        <v>2.212038370778903</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.540915140667309</v>
+        <v>1.521891496955367</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.106836573429278</v>
+        <v>0.1069173365219762</v>
       </c>
       <c r="C83">
-        <v>27.09774688655121</v>
+        <v>26.17179750556191</v>
       </c>
       <c r="D83">
-        <v>90.01474688655121</v>
+        <v>89.89579750556192</v>
       </c>
       <c r="E83">
-        <v>24.267</v>
+        <v>25.07400000000001</v>
       </c>
       <c r="F83">
-        <v>65.367</v>
+        <v>66.17400000000001</v>
       </c>
       <c r="G83">
         <v>2.45</v>
@@ -8087,28 +8087,28 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M83">
-        <v>5.88303</v>
+        <v>5.95566</v>
       </c>
       <c r="N83">
-        <v>3.070303333333333</v>
+        <v>2.997673333333333</v>
       </c>
       <c r="O83">
-        <v>0.7675758333333333</v>
+        <v>0.7494183333333333</v>
       </c>
       <c r="P83">
-        <v>2.3027275</v>
+        <v>2.248255</v>
       </c>
       <c r="Q83">
-        <v>2.4327275</v>
+        <v>2.378255</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2745345969962001</v>
+        <v>0.2864852028998678</v>
       </c>
       <c r="T83">
-        <v>2.212038370778903</v>
+        <v>2.327609863505074</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.521891496955367</v>
+        <v>1.503331844553472</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1069173365219762</v>
+        <v>0.1460920199875609</v>
       </c>
       <c r="C84">
-        <v>26.17179750556191</v>
+        <v>-9.749057142130589</v>
       </c>
       <c r="D84">
-        <v>89.89579750556192</v>
+        <v>54.78194285786942</v>
       </c>
       <c r="E84">
-        <v>25.07400000000001</v>
+        <v>25.88100000000001</v>
       </c>
       <c r="F84">
-        <v>66.17400000000001</v>
+        <v>66.98100000000001</v>
       </c>
       <c r="G84">
         <v>2.45</v>
@@ -8169,45 +8169,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M84">
-        <v>5.95566</v>
+        <v>9.832810800000003</v>
       </c>
       <c r="N84">
-        <v>2.997673333333333</v>
+        <v>-0.8794774666666694</v>
       </c>
       <c r="O84">
-        <v>0.7494183333333333</v>
+        <v>-0.2198693666666673</v>
       </c>
       <c r="P84">
-        <v>2.248255</v>
+        <v>-0.659608100000002</v>
       </c>
       <c r="Q84">
-        <v>2.378255</v>
+        <v>-0.5296081000000021</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2864852028998678</v>
+        <v>0.3057911324680733</v>
       </c>
       <c r="T84">
-        <v>2.327609863505074</v>
+        <v>2.514312957611711</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.25</v>
+        <v>0.2276392151604638</v>
       </c>
       <c r="W84">
-        <v>0.0675</v>
+        <v>0.1133825632144439</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.503331844553472</v>
+        <v>0.9105568606418554</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1460920199875609</v>
+        <v>0.1471020199875609</v>
       </c>
       <c r="C85">
-        <v>-9.749057142130589</v>
+        <v>-11.10224331189546</v>
       </c>
       <c r="D85">
-        <v>54.78194285786942</v>
+        <v>54.23575668810455</v>
       </c>
       <c r="E85">
-        <v>25.88100000000001</v>
+        <v>26.68800000000001</v>
       </c>
       <c r="F85">
-        <v>66.98100000000001</v>
+        <v>67.78800000000001</v>
       </c>
       <c r="G85">
         <v>2.45</v>
@@ -8251,37 +8251,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M85">
-        <v>9.832810800000003</v>
+        <v>9.951278400000003</v>
       </c>
       <c r="N85">
-        <v>-0.8794774666666694</v>
+        <v>-0.99794506666667</v>
       </c>
       <c r="O85">
-        <v>-0.2198693666666673</v>
+        <v>-0.2494862666666675</v>
       </c>
       <c r="P85">
-        <v>-0.659608100000002</v>
+        <v>-0.7484588000000025</v>
       </c>
       <c r="Q85">
-        <v>-0.5296081000000021</v>
+        <v>-0.6184588000000026</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3057911324680733</v>
+        <v>0.3220405782473279</v>
       </c>
       <c r="T85">
-        <v>2.514312957611711</v>
+        <v>2.671457517462444</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2276392151604638</v>
+        <v>0.2249292245037917</v>
       </c>
       <c r="W85">
-        <v>0.1133825632144439</v>
+        <v>0.1137803898428434</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9105568606418554</v>
+        <v>0.8997168980151666</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1471020199875609</v>
+        <v>0.1481120199875609</v>
       </c>
       <c r="C86">
-        <v>-11.10224331189544</v>
+        <v>-12.44464584095942</v>
       </c>
       <c r="D86">
-        <v>54.23575668810455</v>
+        <v>53.70035415904057</v>
       </c>
       <c r="E86">
-        <v>26.688</v>
+        <v>27.495</v>
       </c>
       <c r="F86">
-        <v>67.788</v>
+        <v>68.595</v>
       </c>
       <c r="G86">
         <v>2.45</v>
@@ -8333,37 +8333,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M86">
-        <v>9.9512784</v>
+        <v>10.069746</v>
       </c>
       <c r="N86">
-        <v>-0.9979450666666665</v>
+        <v>-1.116412666666667</v>
       </c>
       <c r="O86">
-        <v>-0.2494862666666666</v>
+        <v>-0.2791031666666668</v>
       </c>
       <c r="P86">
-        <v>-0.7484587999999999</v>
+        <v>-0.8373095000000004</v>
       </c>
       <c r="Q86">
-        <v>-0.6184588</v>
+        <v>-0.7073095000000005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3220405782473277</v>
+        <v>0.3404566167971496</v>
       </c>
       <c r="T86">
-        <v>2.671457517462442</v>
+        <v>2.849554685293271</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2249292245037917</v>
+        <v>0.2222829983331589</v>
       </c>
       <c r="W86">
-        <v>0.1137803898428434</v>
+        <v>0.1141688558446923</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.899716898015167</v>
+        <v>0.8891319933326355</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1481120199875609</v>
+        <v>0.1491220199875609</v>
       </c>
       <c r="C87">
-        <v>-12.44464584095942</v>
+        <v>-13.77658096811975</v>
       </c>
       <c r="D87">
-        <v>53.70035415904057</v>
+        <v>53.17541903188025</v>
       </c>
       <c r="E87">
-        <v>27.495</v>
+        <v>28.302</v>
       </c>
       <c r="F87">
-        <v>68.595</v>
+        <v>69.402</v>
       </c>
       <c r="G87">
         <v>2.45</v>
@@ -8415,37 +8415,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M87">
-        <v>10.069746</v>
+        <v>10.1882136</v>
       </c>
       <c r="N87">
-        <v>-1.116412666666667</v>
+        <v>-1.234880266666668</v>
       </c>
       <c r="O87">
-        <v>-0.2791031666666668</v>
+        <v>-0.308720066666667</v>
       </c>
       <c r="P87">
-        <v>-0.8373095000000004</v>
+        <v>-0.9261602000000009</v>
       </c>
       <c r="Q87">
-        <v>-0.7073095000000005</v>
+        <v>-0.796160200000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3404566167971496</v>
+        <v>0.361503517996946</v>
       </c>
       <c r="T87">
-        <v>2.849554685293271</v>
+        <v>3.053094305671362</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2222829983331589</v>
+        <v>0.2196983123060291</v>
       </c>
       <c r="W87">
-        <v>0.1141688558446923</v>
+        <v>0.1145482877534749</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8891319933326355</v>
+        <v>0.8787932492241164</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1491220199875609</v>
+        <v>0.1501320199875609</v>
       </c>
       <c r="C88">
-        <v>-13.77658096811975</v>
+        <v>-15.09835268660657</v>
       </c>
       <c r="D88">
-        <v>53.17541903188025</v>
+        <v>52.66064731339343</v>
       </c>
       <c r="E88">
-        <v>28.302</v>
+        <v>29.109</v>
       </c>
       <c r="F88">
-        <v>69.402</v>
+        <v>70.209</v>
       </c>
       <c r="G88">
         <v>2.45</v>
@@ -8497,37 +8497,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M88">
-        <v>10.1882136</v>
+        <v>10.3066812</v>
       </c>
       <c r="N88">
-        <v>-1.234880266666668</v>
+        <v>-1.353347866666669</v>
       </c>
       <c r="O88">
-        <v>-0.308720066666667</v>
+        <v>-0.3383369666666671</v>
       </c>
       <c r="P88">
-        <v>-0.9261602000000009</v>
+        <v>-1.015010900000001</v>
       </c>
       <c r="Q88">
-        <v>-0.796160200000001</v>
+        <v>-0.8850109000000015</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.361503517996946</v>
+        <v>0.385788403996711</v>
       </c>
       <c r="T88">
-        <v>3.053094305671362</v>
+        <v>3.287947713799928</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2196983123060291</v>
+        <v>0.2171730443484885</v>
       </c>
       <c r="W88">
-        <v>0.1145482877534749</v>
+        <v>0.1149189970896419</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8787932492241164</v>
+        <v>0.8686921773939541</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1501320199875609</v>
+        <v>0.1511420199875609</v>
       </c>
       <c r="C89">
-        <v>-15.09835268660657</v>
+        <v>-16.41025333112439</v>
       </c>
       <c r="D89">
-        <v>52.66064731339343</v>
+        <v>52.15574666887561</v>
       </c>
       <c r="E89">
-        <v>29.109</v>
+        <v>29.916</v>
       </c>
       <c r="F89">
-        <v>70.209</v>
+        <v>71.01600000000001</v>
       </c>
       <c r="G89">
         <v>2.45</v>
@@ -8579,37 +8579,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M89">
-        <v>10.3066812</v>
+        <v>10.4251488</v>
       </c>
       <c r="N89">
-        <v>-1.353347866666669</v>
+        <v>-1.471815466666669</v>
       </c>
       <c r="O89">
-        <v>-0.3383369666666671</v>
+        <v>-0.3679538666666673</v>
       </c>
       <c r="P89">
-        <v>-1.015010900000001</v>
+        <v>-1.103861600000002</v>
       </c>
       <c r="Q89">
-        <v>-0.8850109000000015</v>
+        <v>-0.973861600000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.385788403996711</v>
+        <v>0.414120770996437</v>
       </c>
       <c r="T89">
-        <v>3.287947713799928</v>
+        <v>3.56194335661659</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2171730443484885</v>
+        <v>0.2147051688445284</v>
       </c>
       <c r="W89">
-        <v>0.1149189970896419</v>
+        <v>0.1152812812136232</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8686921773939541</v>
+        <v>0.8588206753781137</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1511420199875609</v>
+        <v>0.1521520199875609</v>
       </c>
       <c r="C90">
-        <v>-16.41025333112439</v>
+        <v>-17.71256413144324</v>
       </c>
       <c r="D90">
-        <v>52.15574666887561</v>
+        <v>51.66043586855677</v>
       </c>
       <c r="E90">
-        <v>29.916</v>
+        <v>30.72300000000001</v>
       </c>
       <c r="F90">
-        <v>71.01600000000001</v>
+        <v>71.82300000000001</v>
       </c>
       <c r="G90">
         <v>2.45</v>
@@ -8661,37 +8661,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M90">
-        <v>10.4251488</v>
+        <v>10.5436164</v>
       </c>
       <c r="N90">
-        <v>-1.471815466666669</v>
+        <v>-1.590283066666668</v>
       </c>
       <c r="O90">
-        <v>-0.3679538666666673</v>
+        <v>-0.397570766666667</v>
       </c>
       <c r="P90">
-        <v>-1.103861600000002</v>
+        <v>-1.192712300000001</v>
       </c>
       <c r="Q90">
-        <v>-0.973861600000002</v>
+        <v>-1.062712300000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.414120770996437</v>
+        <v>0.4476044774506586</v>
       </c>
       <c r="T90">
-        <v>3.56194335661659</v>
+        <v>3.88575638903628</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2147051688445284</v>
+        <v>0.2122927512170618</v>
       </c>
       <c r="W90">
-        <v>0.1152812812136232</v>
+        <v>0.1156354241213353</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8588206753781137</v>
+        <v>0.8491710048682473</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1521520199875609</v>
+        <v>0.1531620199875609</v>
       </c>
       <c r="C91">
-        <v>-17.71256413144324</v>
+        <v>-19.00555573474287</v>
       </c>
       <c r="D91">
-        <v>51.66043586855677</v>
+        <v>51.17444426525714</v>
       </c>
       <c r="E91">
-        <v>30.72300000000001</v>
+        <v>31.53000000000001</v>
       </c>
       <c r="F91">
-        <v>71.82300000000001</v>
+        <v>72.63000000000001</v>
       </c>
       <c r="G91">
         <v>2.45</v>
@@ -8743,37 +8743,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M91">
-        <v>10.5436164</v>
+        <v>10.662084</v>
       </c>
       <c r="N91">
-        <v>-1.590283066666668</v>
+        <v>-1.708750666666669</v>
       </c>
       <c r="O91">
-        <v>-0.397570766666667</v>
+        <v>-0.4271876666666672</v>
       </c>
       <c r="P91">
-        <v>-1.192712300000001</v>
+        <v>-1.281563000000002</v>
       </c>
       <c r="Q91">
-        <v>-1.062712300000001</v>
+        <v>-1.151563000000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4476044774506586</v>
+        <v>0.4877849251957244</v>
       </c>
       <c r="T91">
-        <v>3.88575638903628</v>
+        <v>4.274332027939908</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2122927512170618</v>
+        <v>0.2099339428702056</v>
       </c>
       <c r="W91">
-        <v>0.1156354241213353</v>
+        <v>0.1159816971866538</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8491710048682473</v>
+        <v>0.8397357714808222</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1531620199875609</v>
+        <v>0.1541720199875609</v>
       </c>
       <c r="C92">
-        <v>-19.00555573474287</v>
+        <v>-20.28948869874818</v>
       </c>
       <c r="D92">
-        <v>51.17444426525714</v>
+        <v>50.69751130125183</v>
       </c>
       <c r="E92">
-        <v>31.53000000000001</v>
+        <v>32.33700000000001</v>
       </c>
       <c r="F92">
-        <v>72.63000000000001</v>
+        <v>73.43700000000001</v>
       </c>
       <c r="G92">
         <v>2.45</v>
@@ -8825,37 +8825,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M92">
-        <v>10.662084</v>
+        <v>10.7805516</v>
       </c>
       <c r="N92">
-        <v>-1.708750666666669</v>
+        <v>-1.827218266666669</v>
       </c>
       <c r="O92">
-        <v>-0.4271876666666672</v>
+        <v>-0.4568045666666674</v>
       </c>
       <c r="P92">
-        <v>-1.281563000000002</v>
+        <v>-1.370413700000002</v>
       </c>
       <c r="Q92">
-        <v>-1.151563000000002</v>
+        <v>-1.240413700000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4877849251957244</v>
+        <v>0.5368943613285827</v>
       </c>
       <c r="T92">
-        <v>4.274332027939908</v>
+        <v>4.74925780882212</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2099339428702056</v>
+        <v>0.2076269764650385</v>
       </c>
       <c r="W92">
-        <v>0.1159816971866538</v>
+        <v>0.1163203598549324</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8397357714808222</v>
+        <v>0.8305079058601539</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1541720199875609</v>
+        <v>0.1551820199875609</v>
       </c>
       <c r="C93">
-        <v>-20.28948869874818</v>
+        <v>-21.56461395754378</v>
       </c>
       <c r="D93">
-        <v>50.69751130125183</v>
+        <v>50.22938604245621</v>
       </c>
       <c r="E93">
-        <v>32.33700000000001</v>
+        <v>33.144</v>
       </c>
       <c r="F93">
-        <v>73.43700000000001</v>
+        <v>74.244</v>
       </c>
       <c r="G93">
         <v>2.45</v>
@@ -8907,37 +8907,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M93">
-        <v>10.7805516</v>
+        <v>10.8990192</v>
       </c>
       <c r="N93">
-        <v>-1.827218266666669</v>
+        <v>-1.945685866666668</v>
       </c>
       <c r="O93">
-        <v>-0.4568045666666674</v>
+        <v>-0.4864214666666671</v>
       </c>
       <c r="P93">
-        <v>-1.370413700000002</v>
+        <v>-1.459264400000001</v>
       </c>
       <c r="Q93">
-        <v>-1.240413700000002</v>
+        <v>-1.329264400000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5368943613285827</v>
+        <v>0.5982811564946557</v>
       </c>
       <c r="T93">
-        <v>4.74925780882212</v>
+        <v>5.342915034924888</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2076269764650385</v>
+        <v>0.205370161503462</v>
       </c>
       <c r="W93">
-        <v>0.1163203598549324</v>
+        <v>0.1166516602912918</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8305079058601539</v>
+        <v>0.821480646013848</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1551820199875609</v>
+        <v>0.1561920199875609</v>
       </c>
       <c r="C94">
-        <v>-21.56461395754378</v>
+        <v>-22.83117326181775</v>
       </c>
       <c r="D94">
-        <v>50.22938604245621</v>
+        <v>49.76982673818225</v>
       </c>
       <c r="E94">
-        <v>33.144</v>
+        <v>33.951</v>
       </c>
       <c r="F94">
-        <v>74.244</v>
+        <v>75.051</v>
       </c>
       <c r="G94">
         <v>2.45</v>
@@ -8989,37 +8989,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M94">
-        <v>10.8990192</v>
+        <v>11.0174868</v>
       </c>
       <c r="N94">
-        <v>-1.945685866666668</v>
+        <v>-2.064153466666669</v>
       </c>
       <c r="O94">
-        <v>-0.4864214666666671</v>
+        <v>-0.5160383666666672</v>
       </c>
       <c r="P94">
-        <v>-1.459264400000001</v>
+        <v>-1.548115100000002</v>
       </c>
       <c r="Q94">
-        <v>-1.329264400000001</v>
+        <v>-1.418115100000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5982811564946557</v>
+        <v>0.6772070359938923</v>
       </c>
       <c r="T94">
-        <v>5.342915034924888</v>
+        <v>6.106188611342729</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.205370161503462</v>
+        <v>0.2031618801969731</v>
       </c>
       <c r="W94">
-        <v>0.1166516602912918</v>
+        <v>0.1169758359870844</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.821480646013848</v>
+        <v>0.8126475207878925</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1561920199875609</v>
+        <v>0.1572020199875609</v>
       </c>
       <c r="C95">
-        <v>-22.83117326181775</v>
+        <v>-24.08939959515693</v>
       </c>
       <c r="D95">
-        <v>49.76982673818225</v>
+        <v>49.31860040484307</v>
       </c>
       <c r="E95">
-        <v>33.951</v>
+        <v>34.758</v>
       </c>
       <c r="F95">
-        <v>75.051</v>
+        <v>75.858</v>
       </c>
       <c r="G95">
         <v>2.45</v>
@@ -9071,37 +9071,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M95">
-        <v>11.0174868</v>
+        <v>11.1359544</v>
       </c>
       <c r="N95">
-        <v>-2.064153466666669</v>
+        <v>-2.182621066666668</v>
       </c>
       <c r="O95">
-        <v>-0.5160383666666672</v>
+        <v>-0.545655266666667</v>
       </c>
       <c r="P95">
-        <v>-1.548115100000002</v>
+        <v>-1.636965800000001</v>
       </c>
       <c r="Q95">
-        <v>-1.418115100000002</v>
+        <v>-1.506965800000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6772070359938923</v>
+        <v>0.7824415419928745</v>
       </c>
       <c r="T95">
-        <v>6.106188611342729</v>
+        <v>7.123886713233185</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2031618801969731</v>
+        <v>0.201000583599133</v>
       </c>
       <c r="W95">
-        <v>0.1169758359870844</v>
+        <v>0.1172931143276473</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8126475207878925</v>
+        <v>0.804002334396532</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1572020199875609</v>
+        <v>0.2122809373265162</v>
       </c>
       <c r="C96">
-        <v>-24.08939959515693</v>
+        <v>-41.21307319511187</v>
       </c>
       <c r="D96">
-        <v>49.31860040484307</v>
+        <v>33.00192680488813</v>
       </c>
       <c r="E96">
-        <v>34.758</v>
+        <v>35.565</v>
       </c>
       <c r="F96">
-        <v>75.858</v>
+        <v>76.66500000000001</v>
       </c>
       <c r="G96">
         <v>2.45</v>
@@ -9153,45 +9153,45 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M96">
-        <v>11.1359544</v>
+        <v>15.394332</v>
       </c>
       <c r="N96">
-        <v>-2.182621066666668</v>
+        <v>-6.440998666666669</v>
       </c>
       <c r="O96">
-        <v>-0.545655266666667</v>
+        <v>-1.610249666666667</v>
       </c>
       <c r="P96">
-        <v>-1.636965800000001</v>
+        <v>-4.830749000000002</v>
       </c>
       <c r="Q96">
-        <v>-1.506965800000001</v>
+        <v>-4.700749000000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7824415419928745</v>
+        <v>0.9851481971705562</v>
       </c>
       <c r="T96">
-        <v>7.123886713233185</v>
+        <v>9.084214993929301</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.201000583599133</v>
+        <v>0.1453998350388528</v>
       </c>
       <c r="W96">
-        <v>0.1172931143276473</v>
+        <v>0.1716037131241984</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.804002334396532</v>
+        <v>0.5815993401554111</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2122809373265162</v>
+        <v>0.2138309373265162</v>
       </c>
       <c r="C97">
-        <v>-41.21307319511187</v>
+        <v>-42.32449919761745</v>
       </c>
       <c r="D97">
-        <v>33.00192680488813</v>
+        <v>32.69750080238256</v>
       </c>
       <c r="E97">
-        <v>35.565</v>
+        <v>36.37200000000001</v>
       </c>
       <c r="F97">
-        <v>76.66500000000001</v>
+        <v>77.47200000000001</v>
       </c>
       <c r="G97">
         <v>2.45</v>
@@ -9235,37 +9235,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M97">
-        <v>15.394332</v>
+        <v>15.5563776</v>
       </c>
       <c r="N97">
-        <v>-6.440998666666669</v>
+        <v>-6.60304426666667</v>
       </c>
       <c r="O97">
-        <v>-1.610249666666667</v>
+        <v>-1.650761066666667</v>
       </c>
       <c r="P97">
-        <v>-4.830749000000002</v>
+        <v>-4.952283200000002</v>
       </c>
       <c r="Q97">
-        <v>-4.700749000000002</v>
+        <v>-4.822283200000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9851481971705562</v>
+        <v>1.219985246463196</v>
       </c>
       <c r="T97">
-        <v>9.084214993929301</v>
+        <v>11.35526874241163</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1453998350388528</v>
+        <v>0.1438852534238647</v>
       </c>
       <c r="W97">
-        <v>0.1716037131241984</v>
+        <v>0.171907841112488</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5815993401554111</v>
+        <v>0.5755410136954591</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2138309373265161</v>
+        <v>0.2153809373265162</v>
       </c>
       <c r="C98">
-        <v>-42.32449919761743</v>
+        <v>-43.43036018425126</v>
       </c>
       <c r="D98">
-        <v>32.69750080238256</v>
+        <v>32.39863981574873</v>
       </c>
       <c r="E98">
-        <v>36.37199999999999</v>
+        <v>37.17899999999999</v>
       </c>
       <c r="F98">
-        <v>77.47199999999999</v>
+        <v>78.279</v>
       </c>
       <c r="G98">
         <v>2.45</v>
@@ -9317,37 +9317,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M98">
-        <v>15.5563776</v>
+        <v>15.7184232</v>
       </c>
       <c r="N98">
-        <v>-6.603044266666666</v>
+        <v>-6.765089866666667</v>
       </c>
       <c r="O98">
-        <v>-1.650761066666667</v>
+        <v>-1.691272466666667</v>
       </c>
       <c r="P98">
-        <v>-4.9522832</v>
+        <v>-5.0738174</v>
       </c>
       <c r="Q98">
-        <v>-4.8222832</v>
+        <v>-4.9438174</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.219985246463193</v>
+        <v>1.61138032861759</v>
       </c>
       <c r="T98">
-        <v>11.3552687424116</v>
+        <v>15.14035832321547</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1438852534238648</v>
+        <v>0.1424019002957837</v>
       </c>
       <c r="W98">
-        <v>0.1719078411124879</v>
+        <v>0.1722056984206067</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5755410136954591</v>
+        <v>0.5696076011831348</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2153809373265162</v>
+        <v>0.2169309373265162</v>
       </c>
       <c r="C99">
-        <v>-43.43036018425126</v>
+        <v>-44.53080736860576</v>
       </c>
       <c r="D99">
-        <v>32.39863981574873</v>
+        <v>32.10519263139424</v>
       </c>
       <c r="E99">
-        <v>37.17899999999999</v>
+        <v>37.986</v>
       </c>
       <c r="F99">
-        <v>78.279</v>
+        <v>79.086</v>
       </c>
       <c r="G99">
         <v>2.45</v>
@@ -9399,37 +9399,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M99">
-        <v>15.7184232</v>
+        <v>15.8804688</v>
       </c>
       <c r="N99">
-        <v>-6.765089866666667</v>
+        <v>-6.927135466666668</v>
       </c>
       <c r="O99">
-        <v>-1.691272466666667</v>
+        <v>-1.731783866666667</v>
       </c>
       <c r="P99">
-        <v>-5.0738174</v>
+        <v>-5.1953516</v>
       </c>
       <c r="Q99">
-        <v>-4.9438174</v>
+        <v>-5.065351600000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.61138032861759</v>
+        <v>2.394170492926385</v>
       </c>
       <c r="T99">
-        <v>15.14035832321547</v>
+        <v>22.7105374848232</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1424019002957837</v>
+        <v>0.1409488196805206</v>
       </c>
       <c r="W99">
-        <v>0.1722056984206067</v>
+        <v>0.1724974770081515</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5696076011831348</v>
+        <v>0.5637952787220823</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2169309373265162</v>
+        <v>0.2184809373265162</v>
       </c>
       <c r="C100">
-        <v>-44.53080736860576</v>
+        <v>-45.62598653504477</v>
       </c>
       <c r="D100">
-        <v>32.10519263139424</v>
+        <v>31.81701346495523</v>
       </c>
       <c r="E100">
-        <v>37.986</v>
+        <v>38.793</v>
       </c>
       <c r="F100">
-        <v>79.086</v>
+        <v>79.893</v>
       </c>
       <c r="G100">
         <v>2.45</v>
@@ -9481,37 +9481,37 @@
         <v>8.953333333333333</v>
       </c>
       <c r="M100">
-        <v>15.8804688</v>
+        <v>16.0425144</v>
       </c>
       <c r="N100">
-        <v>-6.927135466666668</v>
+        <v>-7.089181066666669</v>
       </c>
       <c r="O100">
-        <v>-1.731783866666667</v>
+        <v>-1.772295266666667</v>
       </c>
       <c r="P100">
-        <v>-5.1953516</v>
+        <v>-5.316885800000001</v>
       </c>
       <c r="Q100">
-        <v>-5.065351600000001</v>
+        <v>-5.186885800000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.394170492926385</v>
+        <v>4.742540985852771</v>
       </c>
       <c r="T100">
-        <v>22.7105374848232</v>
+        <v>45.4210749696464</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1409488196805206</v>
+        <v>0.1395250942292022</v>
       </c>
       <c r="W100">
-        <v>0.1724974770081515</v>
+        <v>0.1727833610787762</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5637952787220823</v>
+        <v>0.5581003769168087</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2184809373265162</v>
-      </c>
-      <c r="C101">
-        <v>-45.62598653504477</v>
-      </c>
-      <c r="D101">
-        <v>31.81701346495523</v>
-      </c>
-      <c r="E101">
-        <v>38.793</v>
-      </c>
-      <c r="F101">
-        <v>79.893</v>
-      </c>
-      <c r="G101">
-        <v>2.45</v>
-      </c>
-      <c r="H101">
-        <v>39.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.083333333333334</v>
-      </c>
-      <c r="K101">
-        <v>0.1299999999999999</v>
-      </c>
-      <c r="L101">
-        <v>8.953333333333333</v>
-      </c>
-      <c r="M101">
-        <v>16.0425144</v>
-      </c>
-      <c r="N101">
-        <v>-7.089181066666669</v>
-      </c>
-      <c r="O101">
-        <v>-1.772295266666667</v>
-      </c>
-      <c r="P101">
-        <v>-5.316885800000001</v>
-      </c>
-      <c r="Q101">
-        <v>-5.186885800000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.742540985852771</v>
-      </c>
-      <c r="T101">
-        <v>45.4210749696464</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1395250942292022</v>
-      </c>
-      <c r="W101">
-        <v>0.1727833610787762</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5581003769168087</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
